--- a/templates/ERC000037/metadata_template_ERC000037.xlsx
+++ b/templates/ERC000037/metadata_template_ERC000037.xlsx
@@ -19,15 +19,15 @@
   <definedNames>
     <definedName name="drainageclassification">'cv_sample'!$BF$1:$BF$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BB$1:$BB$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BB$1:$BB$294</definedName>
     <definedName name="growthfacility">'cv_sample'!$T$1:$T$6</definedName>
     <definedName name="growthhabit">'cv_sample'!$AX$1:$AX$4</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="samplecapturestatus">'cv_sample'!$AU$1:$AU$7</definedName>
     <definedName name="samplehealthstate">'cv_sample'!$W$1:$W$2</definedName>
     <definedName name="soiltype">'cv_sample'!$O$1:$O$32</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="828">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1225,7 +1231,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>sampling time point</t>
@@ -1519,9 +1525,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1540,6 +1543,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1741,6 +1747,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1750,9 +1759,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1792,7 +1798,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1861,6 +1867,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1936,6 +1945,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1957,6 +1969,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2002,6 +2017,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2014,6 +2032,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2023,9 +2044,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2050,6 +2068,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2110,12 +2131,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2350,13 +2371,13 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>air temperature regimen</t>
@@ -3027,10 +3048,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3071,10 +3092,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3101,7 +3122,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3118,7 +3139,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3135,7 +3156,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3152,7 +3173,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3169,7 +3190,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3186,7 +3207,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3203,7 +3224,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3220,7 +3241,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3237,7 +3258,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3254,7 +3275,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3268,7 +3289,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3282,7 +3303,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3296,7 +3317,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3310,7 +3331,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3324,7 +3345,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3338,7 +3359,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3352,7 +3373,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3366,7 +3387,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3376,8 +3397,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3388,7 +3412,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3399,7 +3423,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3410,7 +3434,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3421,7 +3445,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3432,7 +3456,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3443,7 +3467,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3454,7 +3478,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3465,7 +3489,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3476,7 +3500,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3487,7 +3511,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3498,7 +3522,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3509,7 +3533,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3520,7 +3544,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3528,7 +3552,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3536,7 +3560,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3544,7 +3568,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3552,7 +3576,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3560,7 +3584,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3568,7 +3592,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3576,7 +3600,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3584,7 +3608,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3592,7 +3616,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3600,236 +3624,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3851,27 +3880,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3891,122 +3920,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4030,630 +4059,630 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
     </row>
     <row r="2" spans="1:105" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -4689,1638 +4718,1663 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:BF289"/>
+  <dimension ref="G1:BF294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:58">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="T1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AU1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AX1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BB1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="BF1" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2" spans="7:58">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="W2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AU2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AX2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BB2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="BF2" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="7:58">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="T3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AU3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AX3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="BB3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="BF3" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="7:58">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="T4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AU4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AX4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BB4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="BF4" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="7:58">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="T5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AU5" t="s">
         <v>116</v>
       </c>
       <c r="BB5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="BF5" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="7:58">
       <c r="O6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="T6" t="s">
         <v>116</v>
       </c>
       <c r="AU6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BB6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BF6" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="7:58">
       <c r="O7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AU7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BB7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="7:58">
       <c r="O8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BB8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="7:58">
       <c r="O9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="BB9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="7:58">
       <c r="O10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="BB10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="7:58">
       <c r="O11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="BB11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="7:58">
       <c r="O12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="BB12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="7:58">
       <c r="O13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="BB13" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="7:58">
       <c r="O14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="BB14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="7:58">
       <c r="O15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="BB15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="7:58">
       <c r="O16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="BB16" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="15:54">
       <c r="O17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="BB17" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" spans="15:54">
       <c r="O18" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="BB18" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="15:54">
       <c r="O19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="BB19" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="15:54">
       <c r="O20" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="BB20" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="15:54">
       <c r="O21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="BB21" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="15:54">
       <c r="O22" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="BB22" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="15:54">
       <c r="O23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="BB23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="15:54">
       <c r="O24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="BB24" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="15:54">
       <c r="O25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="BB25" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="15:54">
       <c r="O26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BB26" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="27" spans="15:54">
       <c r="O27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BB27" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="15:54">
       <c r="O28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BB28" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" spans="15:54">
       <c r="O29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BB29" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" spans="15:54">
       <c r="O30" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BB30" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="15:54">
       <c r="O31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BB31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="15:54">
       <c r="O32" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BB32" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="54:54">
       <c r="BB33" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="54:54">
       <c r="BB34" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="35" spans="54:54">
       <c r="BB35" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="54:54">
       <c r="BB36" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="54:54">
       <c r="BB37" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="54:54">
       <c r="BB38" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="54:54">
       <c r="BB39" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40" spans="54:54">
       <c r="BB40" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="54:54">
       <c r="BB41" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="42" spans="54:54">
       <c r="BB42" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="43" spans="54:54">
       <c r="BB43" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" spans="54:54">
       <c r="BB44" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="54:54">
       <c r="BB45" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="46" spans="54:54">
       <c r="BB46" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" spans="54:54">
       <c r="BB47" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="48" spans="54:54">
       <c r="BB48" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" spans="54:54">
       <c r="BB49" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" spans="54:54">
       <c r="BB50" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="54:54">
       <c r="BB51" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="52" spans="54:54">
       <c r="BB52" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="53" spans="54:54">
       <c r="BB53" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="54" spans="54:54">
       <c r="BB54" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="55" spans="54:54">
       <c r="BB55" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="56" spans="54:54">
       <c r="BB56" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" spans="54:54">
       <c r="BB57" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58" spans="54:54">
       <c r="BB58" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="54:54">
       <c r="BB59" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="60" spans="54:54">
       <c r="BB60" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="54:54">
       <c r="BB61" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="62" spans="54:54">
       <c r="BB62" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="63" spans="54:54">
       <c r="BB63" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64" spans="54:54">
       <c r="BB64" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65" spans="54:54">
       <c r="BB65" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="66" spans="54:54">
       <c r="BB66" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="67" spans="54:54">
       <c r="BB67" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="68" spans="54:54">
       <c r="BB68" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="69" spans="54:54">
       <c r="BB69" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="70" spans="54:54">
       <c r="BB70" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="71" spans="54:54">
       <c r="BB71" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="72" spans="54:54">
       <c r="BB72" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="73" spans="54:54">
       <c r="BB73" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="74" spans="54:54">
       <c r="BB74" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="75" spans="54:54">
       <c r="BB75" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="76" spans="54:54">
       <c r="BB76" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="54:54">
       <c r="BB77" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="54:54">
       <c r="BB78" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="79" spans="54:54">
       <c r="BB79" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="80" spans="54:54">
       <c r="BB80" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="81" spans="54:54">
       <c r="BB81" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="54:54">
       <c r="BB82" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="83" spans="54:54">
       <c r="BB83" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="84" spans="54:54">
       <c r="BB84" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="85" spans="54:54">
       <c r="BB85" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="86" spans="54:54">
       <c r="BB86" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="87" spans="54:54">
       <c r="BB87" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="88" spans="54:54">
       <c r="BB88" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="89" spans="54:54">
       <c r="BB89" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="90" spans="54:54">
       <c r="BB90" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="91" spans="54:54">
       <c r="BB91" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="92" spans="54:54">
       <c r="BB92" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="93" spans="54:54">
       <c r="BB93" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="94" spans="54:54">
       <c r="BB94" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="95" spans="54:54">
       <c r="BB95" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="96" spans="54:54">
       <c r="BB96" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="97" spans="54:54">
       <c r="BB97" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="98" spans="54:54">
       <c r="BB98" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="99" spans="54:54">
       <c r="BB99" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="100" spans="54:54">
       <c r="BB100" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="101" spans="54:54">
       <c r="BB101" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="102" spans="54:54">
       <c r="BB102" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="103" spans="54:54">
       <c r="BB103" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="104" spans="54:54">
       <c r="BB104" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="54:54">
       <c r="BB105" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="106" spans="54:54">
       <c r="BB106" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="107" spans="54:54">
       <c r="BB107" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108" spans="54:54">
       <c r="BB108" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="109" spans="54:54">
       <c r="BB109" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="110" spans="54:54">
       <c r="BB110" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="111" spans="54:54">
       <c r="BB111" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="112" spans="54:54">
       <c r="BB112" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="113" spans="54:54">
       <c r="BB113" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="114" spans="54:54">
       <c r="BB114" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="115" spans="54:54">
       <c r="BB115" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="116" spans="54:54">
       <c r="BB116" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="117" spans="54:54">
       <c r="BB117" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="118" spans="54:54">
       <c r="BB118" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="119" spans="54:54">
       <c r="BB119" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="120" spans="54:54">
       <c r="BB120" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="121" spans="54:54">
       <c r="BB121" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="122" spans="54:54">
       <c r="BB122" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="123" spans="54:54">
       <c r="BB123" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="124" spans="54:54">
       <c r="BB124" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="125" spans="54:54">
       <c r="BB125" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="126" spans="54:54">
       <c r="BB126" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="127" spans="54:54">
       <c r="BB127" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="128" spans="54:54">
       <c r="BB128" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="129" spans="54:54">
       <c r="BB129" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="130" spans="54:54">
       <c r="BB130" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="131" spans="54:54">
       <c r="BB131" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="132" spans="54:54">
       <c r="BB132" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="133" spans="54:54">
       <c r="BB133" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="134" spans="54:54">
       <c r="BB134" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="135" spans="54:54">
       <c r="BB135" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="136" spans="54:54">
       <c r="BB136" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="137" spans="54:54">
       <c r="BB137" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="138" spans="54:54">
       <c r="BB138" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="139" spans="54:54">
       <c r="BB139" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="140" spans="54:54">
       <c r="BB140" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="141" spans="54:54">
       <c r="BB141" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="142" spans="54:54">
       <c r="BB142" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="143" spans="54:54">
       <c r="BB143" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="144" spans="54:54">
       <c r="BB144" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="145" spans="54:54">
       <c r="BB145" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="146" spans="54:54">
       <c r="BB146" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="147" spans="54:54">
       <c r="BB147" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="148" spans="54:54">
       <c r="BB148" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="149" spans="54:54">
       <c r="BB149" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="150" spans="54:54">
       <c r="BB150" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="151" spans="54:54">
       <c r="BB151" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="152" spans="54:54">
       <c r="BB152" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="153" spans="54:54">
       <c r="BB153" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="154" spans="54:54">
       <c r="BB154" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="155" spans="54:54">
       <c r="BB155" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="156" spans="54:54">
       <c r="BB156" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="157" spans="54:54">
       <c r="BB157" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="158" spans="54:54">
       <c r="BB158" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="159" spans="54:54">
       <c r="BB159" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="160" spans="54:54">
       <c r="BB160" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="161" spans="54:54">
       <c r="BB161" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="162" spans="54:54">
       <c r="BB162" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="163" spans="54:54">
       <c r="BB163" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="164" spans="54:54">
       <c r="BB164" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="165" spans="54:54">
       <c r="BB165" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="166" spans="54:54">
       <c r="BB166" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="167" spans="54:54">
       <c r="BB167" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="168" spans="54:54">
       <c r="BB168" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="169" spans="54:54">
       <c r="BB169" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="170" spans="54:54">
       <c r="BB170" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="171" spans="54:54">
       <c r="BB171" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="172" spans="54:54">
       <c r="BB172" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="173" spans="54:54">
       <c r="BB173" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="174" spans="54:54">
       <c r="BB174" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="175" spans="54:54">
       <c r="BB175" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="176" spans="54:54">
       <c r="BB176" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="177" spans="54:54">
       <c r="BB177" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="178" spans="54:54">
       <c r="BB178" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="179" spans="54:54">
       <c r="BB179" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="180" spans="54:54">
       <c r="BB180" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="181" spans="54:54">
       <c r="BB181" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="182" spans="54:54">
       <c r="BB182" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="183" spans="54:54">
       <c r="BB183" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="184" spans="54:54">
       <c r="BB184" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="185" spans="54:54">
       <c r="BB185" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="186" spans="54:54">
       <c r="BB186" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="187" spans="54:54">
       <c r="BB187" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="188" spans="54:54">
       <c r="BB188" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="189" spans="54:54">
       <c r="BB189" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="190" spans="54:54">
       <c r="BB190" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="191" spans="54:54">
       <c r="BB191" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" spans="54:54">
       <c r="BB192" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="193" spans="54:54">
       <c r="BB193" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="194" spans="54:54">
       <c r="BB194" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="195" spans="54:54">
       <c r="BB195" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="196" spans="54:54">
       <c r="BB196" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="197" spans="54:54">
       <c r="BB197" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="198" spans="54:54">
       <c r="BB198" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="199" spans="54:54">
       <c r="BB199" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="200" spans="54:54">
       <c r="BB200" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="201" spans="54:54">
       <c r="BB201" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="202" spans="54:54">
       <c r="BB202" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="203" spans="54:54">
       <c r="BB203" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="204" spans="54:54">
       <c r="BB204" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="205" spans="54:54">
       <c r="BB205" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="206" spans="54:54">
       <c r="BB206" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="207" spans="54:54">
       <c r="BB207" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="208" spans="54:54">
       <c r="BB208" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="209" spans="54:54">
       <c r="BB209" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="210" spans="54:54">
       <c r="BB210" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="211" spans="54:54">
       <c r="BB211" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="212" spans="54:54">
       <c r="BB212" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="213" spans="54:54">
       <c r="BB213" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="214" spans="54:54">
       <c r="BB214" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="215" spans="54:54">
       <c r="BB215" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="216" spans="54:54">
       <c r="BB216" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="217" spans="54:54">
       <c r="BB217" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="218" spans="54:54">
       <c r="BB218" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="219" spans="54:54">
       <c r="BB219" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="220" spans="54:54">
       <c r="BB220" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="54:54">
       <c r="BB221" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="222" spans="54:54">
       <c r="BB222" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="223" spans="54:54">
       <c r="BB223" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="224" spans="54:54">
       <c r="BB224" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="225" spans="54:54">
       <c r="BB225" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="226" spans="54:54">
       <c r="BB226" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="227" spans="54:54">
       <c r="BB227" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="228" spans="54:54">
       <c r="BB228" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="229" spans="54:54">
       <c r="BB229" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="230" spans="54:54">
       <c r="BB230" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="231" spans="54:54">
       <c r="BB231" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="232" spans="54:54">
       <c r="BB232" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="233" spans="54:54">
       <c r="BB233" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="234" spans="54:54">
       <c r="BB234" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="235" spans="54:54">
       <c r="BB235" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="236" spans="54:54">
       <c r="BB236" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="237" spans="54:54">
       <c r="BB237" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="238" spans="54:54">
       <c r="BB238" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="239" spans="54:54">
       <c r="BB239" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="240" spans="54:54">
       <c r="BB240" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="241" spans="54:54">
       <c r="BB241" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="242" spans="54:54">
       <c r="BB242" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="243" spans="54:54">
       <c r="BB243" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="244" spans="54:54">
       <c r="BB244" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="245" spans="54:54">
       <c r="BB245" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="246" spans="54:54">
       <c r="BB246" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="247" spans="54:54">
       <c r="BB247" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="248" spans="54:54">
       <c r="BB248" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="249" spans="54:54">
       <c r="BB249" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="250" spans="54:54">
       <c r="BB250" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="251" spans="54:54">
       <c r="BB251" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="252" spans="54:54">
       <c r="BB252" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="253" spans="54:54">
       <c r="BB253" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="254" spans="54:54">
       <c r="BB254" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="255" spans="54:54">
       <c r="BB255" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="256" spans="54:54">
       <c r="BB256" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="257" spans="54:54">
       <c r="BB257" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="258" spans="54:54">
       <c r="BB258" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="259" spans="54:54">
       <c r="BB259" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="260" spans="54:54">
       <c r="BB260" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="261" spans="54:54">
       <c r="BB261" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="262" spans="54:54">
       <c r="BB262" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="263" spans="54:54">
       <c r="BB263" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="264" spans="54:54">
       <c r="BB264" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="265" spans="54:54">
       <c r="BB265" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="266" spans="54:54">
       <c r="BB266" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="267" spans="54:54">
       <c r="BB267" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="268" spans="54:54">
       <c r="BB268" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="269" spans="54:54">
       <c r="BB269" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="270" spans="54:54">
       <c r="BB270" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="271" spans="54:54">
       <c r="BB271" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="272" spans="54:54">
       <c r="BB272" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="273" spans="54:54">
       <c r="BB273" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="274" spans="54:54">
       <c r="BB274" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="275" spans="54:54">
       <c r="BB275" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="276" spans="54:54">
       <c r="BB276" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="277" spans="54:54">
       <c r="BB277" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="278" spans="54:54">
       <c r="BB278" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="279" spans="54:54">
       <c r="BB279" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="280" spans="54:54">
       <c r="BB280" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="281" spans="54:54">
       <c r="BB281" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="282" spans="54:54">
       <c r="BB282" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="283" spans="54:54">
       <c r="BB283" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="284" spans="54:54">
       <c r="BB284" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="285" spans="54:54">
       <c r="BB285" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="286" spans="54:54">
       <c r="BB286" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="287" spans="54:54">
       <c r="BB287" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="288" spans="54:54">
       <c r="BB288" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="289" spans="54:54">
       <c r="BB289" t="s">
-        <v>710</v>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="290" spans="54:54">
+      <c r="BB290" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="291" spans="54:54">
+      <c r="BB291" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="292" spans="54:54">
+      <c r="BB292" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="293" spans="54:54">
+      <c r="BB293" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="294" spans="54:54">
+      <c r="BB294" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000037/metadata_template_ERC000037.xlsx
+++ b/templates/ERC000037/metadata_template_ERC000037.xlsx
@@ -17,20 +17,20 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="drainageclassification">'cv_sample'!$BD$1:$BD$6</definedName>
+    <definedName name="drainageclassification">'cv_sample'!$BE$1:$BE$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AZ$1:$AZ$289</definedName>
-    <definedName name="growthfacility">'cv_sample'!$R$1:$R$6</definedName>
-    <definedName name="growthhabit">'cv_sample'!$AV$1:$AV$4</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BA$1:$BA$294</definedName>
+    <definedName name="growthfacility">'cv_sample'!$S$1:$S$6</definedName>
+    <definedName name="growthhabit">'cv_sample'!$AW$1:$AW$4</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$E$1:$E$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="samplecapturestatus">'cv_sample'!$AS$1:$AS$7</definedName>
-    <definedName name="samplehealthstate">'cv_sample'!$U$1:$U$2</definedName>
-    <definedName name="soiltype">'cv_sample'!$M$1:$M$32</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="samplecapturestatus">'cv_sample'!$AT$1:$AT$7</definedName>
+    <definedName name="samplehealthstate">'cv_sample'!$V$1:$V$2</definedName>
+    <definedName name="soiltype">'cv_sample'!$N$1:$N$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="826">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -844,6 +850,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1507,9 +1519,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1528,6 +1537,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1729,6 +1741,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1738,9 +1753,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1780,7 +1792,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1849,6 +1861,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1924,6 +1939,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1945,6 +1963,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1990,6 +2011,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2002,6 +2026,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2011,9 +2038,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2038,6 +2062,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2098,10 +2125,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3015,10 +3042,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3059,10 +3086,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3089,7 +3116,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3106,7 +3133,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3123,7 +3150,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3140,7 +3167,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3157,7 +3184,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3174,7 +3201,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3191,7 +3218,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3208,7 +3235,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3225,7 +3252,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3242,7 +3269,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3256,7 +3283,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3270,7 +3297,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3284,7 +3311,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3298,7 +3325,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3312,7 +3339,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3326,7 +3353,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3340,7 +3367,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3354,7 +3381,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3364,8 +3391,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3376,7 +3406,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3387,7 +3417,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3398,7 +3428,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3409,7 +3439,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3420,7 +3450,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3431,7 +3461,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3442,7 +3472,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3453,7 +3483,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3464,7 +3494,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3475,7 +3505,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3486,7 +3516,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3497,7 +3527,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3508,7 +3538,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3516,7 +3546,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3524,7 +3554,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3532,7 +3562,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3540,7 +3570,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3548,7 +3578,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3556,7 +3586,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3564,7 +3594,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3572,7 +3602,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3580,7 +3610,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3588,236 +3618,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3839,27 +3874,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3879,122 +3914,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4004,13 +4039,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CY2"/>
+  <dimension ref="A1:CZ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:103">
+    <row r="1" spans="1:104">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4018,644 +4053,650 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>707</v>
+        <v>420</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="2" spans="1:103" ht="150" customHeight="1">
+        <v>822</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="2" spans="1:104" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>708</v>
+        <v>421</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
+      </c>
+      <c r="CZ2" s="2" t="s">
+        <v>825</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
       <formula1>growthfacility</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
       <formula1>samplehealthstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
       <formula1>samplecapturestatus</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
       <formula1>growthhabit</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ3:AZ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA3:BA101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD3:BD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE3:BE101">
       <formula1>drainageclassification</formula1>
     </dataValidation>
   </dataValidations>
@@ -4665,1638 +4706,1663 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:BD289"/>
+  <dimension ref="F1:BE294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:56">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
-      <c r="M1" t="s">
-        <v>291</v>
-      </c>
-      <c r="R1" t="s">
-        <v>333</v>
-      </c>
-      <c r="U1" t="s">
-        <v>344</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>394</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>406</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>418</v>
-      </c>
-      <c r="BD1" t="s">
+    <row r="1" spans="6:57">
+      <c r="F1" t="s">
+        <v>274</v>
+      </c>
+      <c r="N1" t="s">
+        <v>295</v>
+      </c>
+      <c r="S1" t="s">
+        <v>337</v>
+      </c>
+      <c r="V1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>410</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>422</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="2" spans="6:57">
+      <c r="F2" t="s">
+        <v>275</v>
+      </c>
+      <c r="N2" t="s">
+        <v>296</v>
+      </c>
+      <c r="S2" t="s">
+        <v>338</v>
+      </c>
+      <c r="V2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>411</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>423</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="3" spans="6:57">
+      <c r="F3" t="s">
+        <v>276</v>
+      </c>
+      <c r="N3" t="s">
+        <v>297</v>
+      </c>
+      <c r="S3" t="s">
+        <v>339</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>412</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>424</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="4" spans="6:57">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="N4" t="s">
+        <v>298</v>
+      </c>
+      <c r="S4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>401</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>413</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>425</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="5" spans="6:57">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="N5" t="s">
+        <v>299</v>
+      </c>
+      <c r="S5" t="s">
+        <v>341</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>426</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="6" spans="6:57">
+      <c r="N6" t="s">
+        <v>300</v>
+      </c>
+      <c r="S6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>402</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>427</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="7" spans="6:57">
+      <c r="N7" t="s">
+        <v>301</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>403</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="8" spans="6:57">
+      <c r="N8" t="s">
+        <v>302</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="9" spans="6:57">
+      <c r="N9" t="s">
+        <v>303</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="6:57">
+      <c r="N10" t="s">
+        <v>304</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="6:57">
+      <c r="N11" t="s">
+        <v>305</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="12" spans="6:57">
+      <c r="N12" t="s">
+        <v>306</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" spans="6:57">
+      <c r="N13" t="s">
+        <v>307</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="14" spans="6:57">
+      <c r="N14" t="s">
+        <v>308</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="15" spans="6:57">
+      <c r="N15" t="s">
+        <v>309</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" spans="6:57">
+      <c r="N16" t="s">
+        <v>310</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="17" spans="14:53">
+      <c r="N17" t="s">
+        <v>311</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="14:53">
+      <c r="N18" t="s">
+        <v>312</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="19" spans="14:53">
+      <c r="N19" t="s">
+        <v>313</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="20" spans="14:53">
+      <c r="N20" t="s">
+        <v>314</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21" spans="14:53">
+      <c r="N21" t="s">
+        <v>315</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="22" spans="14:53">
+      <c r="N22" t="s">
+        <v>316</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="14:53">
+      <c r="N23" t="s">
+        <v>317</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="14:53">
+      <c r="N24" t="s">
+        <v>318</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="25" spans="14:53">
+      <c r="N25" t="s">
+        <v>319</v>
+      </c>
+      <c r="BA25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" spans="14:53">
+      <c r="N26" t="s">
+        <v>320</v>
+      </c>
+      <c r="BA26" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="27" spans="14:53">
+      <c r="N27" t="s">
+        <v>321</v>
+      </c>
+      <c r="BA27" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="14:53">
+      <c r="N28" t="s">
+        <v>322</v>
+      </c>
+      <c r="BA28" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="29" spans="14:53">
+      <c r="N29" t="s">
+        <v>323</v>
+      </c>
+      <c r="BA29" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="30" spans="14:53">
+      <c r="N30" t="s">
+        <v>324</v>
+      </c>
+      <c r="BA30" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="31" spans="14:53">
+      <c r="N31" t="s">
+        <v>325</v>
+      </c>
+      <c r="BA31" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="32" spans="14:53">
+      <c r="N32" t="s">
+        <v>326</v>
+      </c>
+      <c r="BA32" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="33" spans="53:53">
+      <c r="BA33" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="34" spans="53:53">
+      <c r="BA34" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="35" spans="53:53">
+      <c r="BA35" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="36" spans="53:53">
+      <c r="BA36" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="37" spans="53:53">
+      <c r="BA37" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="38" spans="53:53">
+      <c r="BA38" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="39" spans="53:53">
+      <c r="BA39" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="40" spans="53:53">
+      <c r="BA40" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="41" spans="53:53">
+      <c r="BA41" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="42" spans="53:53">
+      <c r="BA42" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="43" spans="53:53">
+      <c r="BA43" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="44" spans="53:53">
+      <c r="BA44" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="45" spans="53:53">
+      <c r="BA45" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="46" spans="53:53">
+      <c r="BA46" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="47" spans="53:53">
+      <c r="BA47" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="48" spans="53:53">
+      <c r="BA48" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="49" spans="53:53">
+      <c r="BA49" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="50" spans="53:53">
+      <c r="BA50" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="51" spans="53:53">
+      <c r="BA51" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="52" spans="53:53">
+      <c r="BA52" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="53" spans="53:53">
+      <c r="BA53" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="54" spans="53:53">
+      <c r="BA54" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="55" spans="53:53">
+      <c r="BA55" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="56" spans="53:53">
+      <c r="BA56" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="57" spans="53:53">
+      <c r="BA57" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="58" spans="53:53">
+      <c r="BA58" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="59" spans="53:53">
+      <c r="BA59" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="60" spans="53:53">
+      <c r="BA60" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="61" spans="53:53">
+      <c r="BA61" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="62" spans="53:53">
+      <c r="BA62" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="63" spans="53:53">
+      <c r="BA63" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="64" spans="53:53">
+      <c r="BA64" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="65" spans="53:53">
+      <c r="BA65" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="66" spans="53:53">
+      <c r="BA66" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="67" spans="53:53">
+      <c r="BA67" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="68" spans="53:53">
+      <c r="BA68" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="69" spans="53:53">
+      <c r="BA69" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="70" spans="53:53">
+      <c r="BA70" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="71" spans="53:53">
+      <c r="BA71" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="72" spans="53:53">
+      <c r="BA72" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="73" spans="53:53">
+      <c r="BA73" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="74" spans="53:53">
+      <c r="BA74" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="75" spans="53:53">
+      <c r="BA75" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="76" spans="53:53">
+      <c r="BA76" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="77" spans="53:53">
+      <c r="BA77" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="78" spans="53:53">
+      <c r="BA78" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="79" spans="53:53">
+      <c r="BA79" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="80" spans="53:53">
+      <c r="BA80" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="81" spans="53:53">
+      <c r="BA81" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="82" spans="53:53">
+      <c r="BA82" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="83" spans="53:53">
+      <c r="BA83" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="84" spans="53:53">
+      <c r="BA84" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="85" spans="53:53">
+      <c r="BA85" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="86" spans="53:53">
+      <c r="BA86" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="87" spans="53:53">
+      <c r="BA87" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="88" spans="53:53">
+      <c r="BA88" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="89" spans="53:53">
+      <c r="BA89" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="90" spans="53:53">
+      <c r="BA90" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="91" spans="53:53">
+      <c r="BA91" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="92" spans="53:53">
+      <c r="BA92" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="93" spans="53:53">
+      <c r="BA93" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="94" spans="53:53">
+      <c r="BA94" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="95" spans="53:53">
+      <c r="BA95" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="96" spans="53:53">
+      <c r="BA96" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="97" spans="53:53">
+      <c r="BA97" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="98" spans="53:53">
+      <c r="BA98" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="99" spans="53:53">
+      <c r="BA99" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="100" spans="53:53">
+      <c r="BA100" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="101" spans="53:53">
+      <c r="BA101" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="102" spans="53:53">
+      <c r="BA102" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="103" spans="53:53">
+      <c r="BA103" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="104" spans="53:53">
+      <c r="BA104" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="105" spans="53:53">
+      <c r="BA105" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="106" spans="53:53">
+      <c r="BA106" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="107" spans="53:53">
+      <c r="BA107" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="108" spans="53:53">
+      <c r="BA108" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="109" spans="53:53">
+      <c r="BA109" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="110" spans="53:53">
+      <c r="BA110" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="111" spans="53:53">
+      <c r="BA111" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="112" spans="53:53">
+      <c r="BA112" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="113" spans="53:53">
+      <c r="BA113" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="114" spans="53:53">
+      <c r="BA114" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="115" spans="53:53">
+      <c r="BA115" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="116" spans="53:53">
+      <c r="BA116" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="117" spans="53:53">
+      <c r="BA117" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="118" spans="53:53">
+      <c r="BA118" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="119" spans="53:53">
+      <c r="BA119" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="120" spans="53:53">
+      <c r="BA120" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="121" spans="53:53">
+      <c r="BA121" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="122" spans="53:53">
+      <c r="BA122" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="123" spans="53:53">
+      <c r="BA123" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="124" spans="53:53">
+      <c r="BA124" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="125" spans="53:53">
+      <c r="BA125" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="126" spans="53:53">
+      <c r="BA126" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="127" spans="53:53">
+      <c r="BA127" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="128" spans="53:53">
+      <c r="BA128" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="129" spans="53:53">
+      <c r="BA129" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="130" spans="53:53">
+      <c r="BA130" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="131" spans="53:53">
+      <c r="BA131" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="132" spans="53:53">
+      <c r="BA132" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="133" spans="53:53">
+      <c r="BA133" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="134" spans="53:53">
+      <c r="BA134" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="135" spans="53:53">
+      <c r="BA135" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="136" spans="53:53">
+      <c r="BA136" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="137" spans="53:53">
+      <c r="BA137" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="138" spans="53:53">
+      <c r="BA138" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="139" spans="53:53">
+      <c r="BA139" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="140" spans="53:53">
+      <c r="BA140" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="141" spans="53:53">
+      <c r="BA141" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="142" spans="53:53">
+      <c r="BA142" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="143" spans="53:53">
+      <c r="BA143" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="144" spans="53:53">
+      <c r="BA144" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="145" spans="53:53">
+      <c r="BA145" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="146" spans="53:53">
+      <c r="BA146" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="147" spans="53:53">
+      <c r="BA147" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="148" spans="53:53">
+      <c r="BA148" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="149" spans="53:53">
+      <c r="BA149" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="150" spans="53:53">
+      <c r="BA150" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="151" spans="53:53">
+      <c r="BA151" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="152" spans="53:53">
+      <c r="BA152" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="153" spans="53:53">
+      <c r="BA153" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="154" spans="53:53">
+      <c r="BA154" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="155" spans="53:53">
+      <c r="BA155" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="156" spans="53:53">
+      <c r="BA156" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="157" spans="53:53">
+      <c r="BA157" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="158" spans="53:53">
+      <c r="BA158" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="159" spans="53:53">
+      <c r="BA159" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="160" spans="53:53">
+      <c r="BA160" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="161" spans="53:53">
+      <c r="BA161" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="162" spans="53:53">
+      <c r="BA162" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="163" spans="53:53">
+      <c r="BA163" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="164" spans="53:53">
+      <c r="BA164" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="165" spans="53:53">
+      <c r="BA165" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="166" spans="53:53">
+      <c r="BA166" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="167" spans="53:53">
+      <c r="BA167" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="168" spans="53:53">
+      <c r="BA168" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="169" spans="53:53">
+      <c r="BA169" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="170" spans="53:53">
+      <c r="BA170" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="171" spans="53:53">
+      <c r="BA171" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="172" spans="53:53">
+      <c r="BA172" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="173" spans="53:53">
+      <c r="BA173" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="174" spans="53:53">
+      <c r="BA174" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="175" spans="53:53">
+      <c r="BA175" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="176" spans="53:53">
+      <c r="BA176" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="177" spans="53:53">
+      <c r="BA177" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="178" spans="53:53">
+      <c r="BA178" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="179" spans="53:53">
+      <c r="BA179" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="180" spans="53:53">
+      <c r="BA180" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="181" spans="53:53">
+      <c r="BA181" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="182" spans="53:53">
+      <c r="BA182" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="183" spans="53:53">
+      <c r="BA183" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="184" spans="53:53">
+      <c r="BA184" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="185" spans="53:53">
+      <c r="BA185" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="186" spans="53:53">
+      <c r="BA186" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="187" spans="53:53">
+      <c r="BA187" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="188" spans="53:53">
+      <c r="BA188" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="189" spans="53:53">
+      <c r="BA189" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="190" spans="53:53">
+      <c r="BA190" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="191" spans="53:53">
+      <c r="BA191" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="192" spans="53:53">
+      <c r="BA192" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="193" spans="53:53">
+      <c r="BA193" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="194" spans="53:53">
+      <c r="BA194" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="195" spans="53:53">
+      <c r="BA195" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="196" spans="53:53">
+      <c r="BA196" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="197" spans="53:53">
+      <c r="BA197" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="198" spans="53:53">
+      <c r="BA198" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="199" spans="53:53">
+      <c r="BA199" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="200" spans="53:53">
+      <c r="BA200" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="201" spans="53:53">
+      <c r="BA201" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="202" spans="53:53">
+      <c r="BA202" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="203" spans="53:53">
+      <c r="BA203" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="204" spans="53:53">
+      <c r="BA204" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="205" spans="53:53">
+      <c r="BA205" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="206" spans="53:53">
+      <c r="BA206" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="207" spans="53:53">
+      <c r="BA207" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="208" spans="53:53">
+      <c r="BA208" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="209" spans="53:53">
+      <c r="BA209" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="210" spans="53:53">
+      <c r="BA210" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="211" spans="53:53">
+      <c r="BA211" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="212" spans="53:53">
+      <c r="BA212" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="213" spans="53:53">
+      <c r="BA213" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="214" spans="53:53">
+      <c r="BA214" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="215" spans="53:53">
+      <c r="BA215" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="216" spans="53:53">
+      <c r="BA216" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="217" spans="53:53">
+      <c r="BA217" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="218" spans="53:53">
+      <c r="BA218" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="219" spans="53:53">
+      <c r="BA219" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="220" spans="53:53">
+      <c r="BA220" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="221" spans="53:53">
+      <c r="BA221" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="222" spans="53:53">
+      <c r="BA222" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="223" spans="53:53">
+      <c r="BA223" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="224" spans="53:53">
+      <c r="BA224" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="225" spans="53:53">
+      <c r="BA225" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="226" spans="53:53">
+      <c r="BA226" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="227" spans="53:53">
+      <c r="BA227" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="228" spans="53:53">
+      <c r="BA228" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="229" spans="53:53">
+      <c r="BA229" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="230" spans="53:53">
+      <c r="BA230" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="231" spans="53:53">
+      <c r="BA231" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="232" spans="53:53">
+      <c r="BA232" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="233" spans="53:53">
+      <c r="BA233" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="234" spans="53:53">
+      <c r="BA234" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="235" spans="53:53">
+      <c r="BA235" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="236" spans="53:53">
+      <c r="BA236" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="237" spans="53:53">
+      <c r="BA237" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="238" spans="53:53">
+      <c r="BA238" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="239" spans="53:53">
+      <c r="BA239" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="240" spans="53:53">
+      <c r="BA240" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="241" spans="53:53">
+      <c r="BA241" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="242" spans="53:53">
+      <c r="BA242" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="243" spans="53:53">
+      <c r="BA243" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="244" spans="53:53">
+      <c r="BA244" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="245" spans="53:53">
+      <c r="BA245" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="246" spans="53:53">
+      <c r="BA246" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="247" spans="53:53">
+      <c r="BA247" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="248" spans="53:53">
+      <c r="BA248" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="249" spans="53:53">
+      <c r="BA249" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="250" spans="53:53">
+      <c r="BA250" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="251" spans="53:53">
+      <c r="BA251" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="252" spans="53:53">
+      <c r="BA252" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="253" spans="53:53">
+      <c r="BA253" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="254" spans="53:53">
+      <c r="BA254" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="255" spans="53:53">
+      <c r="BA255" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="256" spans="53:53">
+      <c r="BA256" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="257" spans="53:53">
+      <c r="BA257" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="258" spans="53:53">
+      <c r="BA258" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="259" spans="53:53">
+      <c r="BA259" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="260" spans="53:53">
+      <c r="BA260" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="261" spans="53:53">
+      <c r="BA261" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="262" spans="53:53">
+      <c r="BA262" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="263" spans="53:53">
+      <c r="BA263" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="264" spans="53:53">
+      <c r="BA264" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="265" spans="53:53">
+      <c r="BA265" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="266" spans="53:53">
+      <c r="BA266" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="267" spans="53:53">
+      <c r="BA267" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="268" spans="53:53">
+      <c r="BA268" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="269" spans="53:53">
+      <c r="BA269" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="270" spans="53:53">
+      <c r="BA270" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="271" spans="53:53">
+      <c r="BA271" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="272" spans="53:53">
+      <c r="BA272" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="273" spans="53:53">
+      <c r="BA273" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="274" spans="53:53">
+      <c r="BA274" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="275" spans="53:53">
+      <c r="BA275" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="276" spans="53:53">
+      <c r="BA276" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="277" spans="53:53">
+      <c r="BA277" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="278" spans="53:53">
+      <c r="BA278" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="279" spans="53:53">
+      <c r="BA279" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="280" spans="53:53">
+      <c r="BA280" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="281" spans="53:53">
+      <c r="BA281" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="282" spans="53:53">
+      <c r="BA282" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="283" spans="53:53">
+      <c r="BA283" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="284" spans="53:53">
+      <c r="BA284" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="285" spans="53:53">
+      <c r="BA285" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="286" spans="53:53">
+      <c r="BA286" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="287" spans="53:53">
+      <c r="BA287" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="288" spans="53:53">
+      <c r="BA288" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="289" spans="53:53">
+      <c r="BA289" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="290" spans="53:53">
+      <c r="BA290" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="291" spans="53:53">
+      <c r="BA291" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="292" spans="53:53">
+      <c r="BA292" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="293" spans="53:53">
+      <c r="BA293" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="294" spans="53:53">
+      <c r="BA294" t="s">
         <v>715</v>
-      </c>
-    </row>
-    <row r="2" spans="5:56">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M2" t="s">
-        <v>292</v>
-      </c>
-      <c r="R2" t="s">
-        <v>334</v>
-      </c>
-      <c r="U2" t="s">
-        <v>345</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>407</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>419</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="3" spans="5:56">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="M3" t="s">
-        <v>293</v>
-      </c>
-      <c r="R3" t="s">
-        <v>335</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>396</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>408</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>420</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="4" spans="5:56">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="M4" t="s">
-        <v>294</v>
-      </c>
-      <c r="R4" t="s">
-        <v>336</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>397</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>409</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>421</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="5" spans="5:56">
-      <c r="E5" t="s">
-        <v>274</v>
-      </c>
-      <c r="M5" t="s">
-        <v>295</v>
-      </c>
-      <c r="R5" t="s">
-        <v>337</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>422</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="6" spans="5:56">
-      <c r="M6" t="s">
-        <v>296</v>
-      </c>
-      <c r="R6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>398</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>423</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="7" spans="5:56">
-      <c r="M7" t="s">
-        <v>297</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>399</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="8" spans="5:56">
-      <c r="M8" t="s">
-        <v>298</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="9" spans="5:56">
-      <c r="M9" t="s">
-        <v>299</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="10" spans="5:56">
-      <c r="M10" t="s">
-        <v>300</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="11" spans="5:56">
-      <c r="M11" t="s">
-        <v>301</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="12" spans="5:56">
-      <c r="M12" t="s">
-        <v>302</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="13" spans="5:56">
-      <c r="M13" t="s">
-        <v>303</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="14" spans="5:56">
-      <c r="M14" t="s">
-        <v>304</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="15" spans="5:56">
-      <c r="M15" t="s">
-        <v>305</v>
-      </c>
-      <c r="AZ15" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="16" spans="5:56">
-      <c r="M16" t="s">
-        <v>306</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="17" spans="13:52">
-      <c r="M17" t="s">
-        <v>307</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="18" spans="13:52">
-      <c r="M18" t="s">
-        <v>308</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="19" spans="13:52">
-      <c r="M19" t="s">
-        <v>309</v>
-      </c>
-      <c r="AZ19" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="20" spans="13:52">
-      <c r="M20" t="s">
-        <v>310</v>
-      </c>
-      <c r="AZ20" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="21" spans="13:52">
-      <c r="M21" t="s">
-        <v>311</v>
-      </c>
-      <c r="AZ21" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="22" spans="13:52">
-      <c r="M22" t="s">
-        <v>312</v>
-      </c>
-      <c r="AZ22" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="23" spans="13:52">
-      <c r="M23" t="s">
-        <v>313</v>
-      </c>
-      <c r="AZ23" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="24" spans="13:52">
-      <c r="M24" t="s">
-        <v>314</v>
-      </c>
-      <c r="AZ24" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="25" spans="13:52">
-      <c r="M25" t="s">
-        <v>315</v>
-      </c>
-      <c r="AZ25" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="26" spans="13:52">
-      <c r="M26" t="s">
-        <v>316</v>
-      </c>
-      <c r="AZ26" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="27" spans="13:52">
-      <c r="M27" t="s">
-        <v>317</v>
-      </c>
-      <c r="AZ27" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="28" spans="13:52">
-      <c r="M28" t="s">
-        <v>318</v>
-      </c>
-      <c r="AZ28" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="29" spans="13:52">
-      <c r="M29" t="s">
-        <v>319</v>
-      </c>
-      <c r="AZ29" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="30" spans="13:52">
-      <c r="M30" t="s">
-        <v>320</v>
-      </c>
-      <c r="AZ30" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="31" spans="13:52">
-      <c r="M31" t="s">
-        <v>321</v>
-      </c>
-      <c r="AZ31" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="32" spans="13:52">
-      <c r="M32" t="s">
-        <v>322</v>
-      </c>
-      <c r="AZ32" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="33" spans="52:52">
-      <c r="AZ33" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="34" spans="52:52">
-      <c r="AZ34" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="35" spans="52:52">
-      <c r="AZ35" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="36" spans="52:52">
-      <c r="AZ36" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="37" spans="52:52">
-      <c r="AZ37" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="38" spans="52:52">
-      <c r="AZ38" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="39" spans="52:52">
-      <c r="AZ39" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="40" spans="52:52">
-      <c r="AZ40" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="41" spans="52:52">
-      <c r="AZ41" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="42" spans="52:52">
-      <c r="AZ42" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="43" spans="52:52">
-      <c r="AZ43" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="44" spans="52:52">
-      <c r="AZ44" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="45" spans="52:52">
-      <c r="AZ45" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="46" spans="52:52">
-      <c r="AZ46" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="47" spans="52:52">
-      <c r="AZ47" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="48" spans="52:52">
-      <c r="AZ48" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="49" spans="52:52">
-      <c r="AZ49" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="50" spans="52:52">
-      <c r="AZ50" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="51" spans="52:52">
-      <c r="AZ51" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="52" spans="52:52">
-      <c r="AZ52" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="53" spans="52:52">
-      <c r="AZ53" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="54" spans="52:52">
-      <c r="AZ54" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="55" spans="52:52">
-      <c r="AZ55" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="56" spans="52:52">
-      <c r="AZ56" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="57" spans="52:52">
-      <c r="AZ57" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="58" spans="52:52">
-      <c r="AZ58" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="59" spans="52:52">
-      <c r="AZ59" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="60" spans="52:52">
-      <c r="AZ60" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="61" spans="52:52">
-      <c r="AZ61" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="62" spans="52:52">
-      <c r="AZ62" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="63" spans="52:52">
-      <c r="AZ63" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="64" spans="52:52">
-      <c r="AZ64" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="65" spans="52:52">
-      <c r="AZ65" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="66" spans="52:52">
-      <c r="AZ66" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="67" spans="52:52">
-      <c r="AZ67" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="68" spans="52:52">
-      <c r="AZ68" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="69" spans="52:52">
-      <c r="AZ69" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="70" spans="52:52">
-      <c r="AZ70" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="71" spans="52:52">
-      <c r="AZ71" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="72" spans="52:52">
-      <c r="AZ72" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="73" spans="52:52">
-      <c r="AZ73" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="74" spans="52:52">
-      <c r="AZ74" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="75" spans="52:52">
-      <c r="AZ75" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="76" spans="52:52">
-      <c r="AZ76" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="77" spans="52:52">
-      <c r="AZ77" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="78" spans="52:52">
-      <c r="AZ78" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="79" spans="52:52">
-      <c r="AZ79" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="80" spans="52:52">
-      <c r="AZ80" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="81" spans="52:52">
-      <c r="AZ81" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="82" spans="52:52">
-      <c r="AZ82" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="83" spans="52:52">
-      <c r="AZ83" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="84" spans="52:52">
-      <c r="AZ84" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="85" spans="52:52">
-      <c r="AZ85" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="86" spans="52:52">
-      <c r="AZ86" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="87" spans="52:52">
-      <c r="AZ87" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="88" spans="52:52">
-      <c r="AZ88" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="89" spans="52:52">
-      <c r="AZ89" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="90" spans="52:52">
-      <c r="AZ90" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="91" spans="52:52">
-      <c r="AZ91" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="92" spans="52:52">
-      <c r="AZ92" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="93" spans="52:52">
-      <c r="AZ93" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="94" spans="52:52">
-      <c r="AZ94" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="95" spans="52:52">
-      <c r="AZ95" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="96" spans="52:52">
-      <c r="AZ96" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="97" spans="52:52">
-      <c r="AZ97" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="98" spans="52:52">
-      <c r="AZ98" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="99" spans="52:52">
-      <c r="AZ99" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="100" spans="52:52">
-      <c r="AZ100" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="101" spans="52:52">
-      <c r="AZ101" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="102" spans="52:52">
-      <c r="AZ102" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="103" spans="52:52">
-      <c r="AZ103" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="104" spans="52:52">
-      <c r="AZ104" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="105" spans="52:52">
-      <c r="AZ105" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="106" spans="52:52">
-      <c r="AZ106" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="107" spans="52:52">
-      <c r="AZ107" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="108" spans="52:52">
-      <c r="AZ108" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="109" spans="52:52">
-      <c r="AZ109" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="110" spans="52:52">
-      <c r="AZ110" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="111" spans="52:52">
-      <c r="AZ111" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="112" spans="52:52">
-      <c r="AZ112" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="113" spans="52:52">
-      <c r="AZ113" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="114" spans="52:52">
-      <c r="AZ114" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="115" spans="52:52">
-      <c r="AZ115" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="116" spans="52:52">
-      <c r="AZ116" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="117" spans="52:52">
-      <c r="AZ117" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="118" spans="52:52">
-      <c r="AZ118" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="119" spans="52:52">
-      <c r="AZ119" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="120" spans="52:52">
-      <c r="AZ120" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="121" spans="52:52">
-      <c r="AZ121" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="122" spans="52:52">
-      <c r="AZ122" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="123" spans="52:52">
-      <c r="AZ123" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="124" spans="52:52">
-      <c r="AZ124" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="125" spans="52:52">
-      <c r="AZ125" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="126" spans="52:52">
-      <c r="AZ126" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="127" spans="52:52">
-      <c r="AZ127" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="128" spans="52:52">
-      <c r="AZ128" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="129" spans="52:52">
-      <c r="AZ129" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="130" spans="52:52">
-      <c r="AZ130" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="131" spans="52:52">
-      <c r="AZ131" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="132" spans="52:52">
-      <c r="AZ132" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="133" spans="52:52">
-      <c r="AZ133" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="134" spans="52:52">
-      <c r="AZ134" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="135" spans="52:52">
-      <c r="AZ135" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="136" spans="52:52">
-      <c r="AZ136" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="137" spans="52:52">
-      <c r="AZ137" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="138" spans="52:52">
-      <c r="AZ138" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="139" spans="52:52">
-      <c r="AZ139" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="140" spans="52:52">
-      <c r="AZ140" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="141" spans="52:52">
-      <c r="AZ141" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="142" spans="52:52">
-      <c r="AZ142" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="143" spans="52:52">
-      <c r="AZ143" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="144" spans="52:52">
-      <c r="AZ144" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="145" spans="52:52">
-      <c r="AZ145" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="146" spans="52:52">
-      <c r="AZ146" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="147" spans="52:52">
-      <c r="AZ147" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="148" spans="52:52">
-      <c r="AZ148" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="149" spans="52:52">
-      <c r="AZ149" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="150" spans="52:52">
-      <c r="AZ150" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="151" spans="52:52">
-      <c r="AZ151" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="152" spans="52:52">
-      <c r="AZ152" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="153" spans="52:52">
-      <c r="AZ153" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="154" spans="52:52">
-      <c r="AZ154" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="155" spans="52:52">
-      <c r="AZ155" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="156" spans="52:52">
-      <c r="AZ156" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="157" spans="52:52">
-      <c r="AZ157" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="158" spans="52:52">
-      <c r="AZ158" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="159" spans="52:52">
-      <c r="AZ159" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="160" spans="52:52">
-      <c r="AZ160" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="161" spans="52:52">
-      <c r="AZ161" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="162" spans="52:52">
-      <c r="AZ162" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="163" spans="52:52">
-      <c r="AZ163" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="164" spans="52:52">
-      <c r="AZ164" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="165" spans="52:52">
-      <c r="AZ165" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="166" spans="52:52">
-      <c r="AZ166" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="167" spans="52:52">
-      <c r="AZ167" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="168" spans="52:52">
-      <c r="AZ168" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="169" spans="52:52">
-      <c r="AZ169" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="170" spans="52:52">
-      <c r="AZ170" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="171" spans="52:52">
-      <c r="AZ171" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="172" spans="52:52">
-      <c r="AZ172" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="173" spans="52:52">
-      <c r="AZ173" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="174" spans="52:52">
-      <c r="AZ174" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="175" spans="52:52">
-      <c r="AZ175" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="176" spans="52:52">
-      <c r="AZ176" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="177" spans="52:52">
-      <c r="AZ177" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="178" spans="52:52">
-      <c r="AZ178" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="179" spans="52:52">
-      <c r="AZ179" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="180" spans="52:52">
-      <c r="AZ180" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="181" spans="52:52">
-      <c r="AZ181" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="182" spans="52:52">
-      <c r="AZ182" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="183" spans="52:52">
-      <c r="AZ183" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="184" spans="52:52">
-      <c r="AZ184" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="185" spans="52:52">
-      <c r="AZ185" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="186" spans="52:52">
-      <c r="AZ186" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="187" spans="52:52">
-      <c r="AZ187" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="188" spans="52:52">
-      <c r="AZ188" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="189" spans="52:52">
-      <c r="AZ189" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="190" spans="52:52">
-      <c r="AZ190" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="191" spans="52:52">
-      <c r="AZ191" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="192" spans="52:52">
-      <c r="AZ192" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="193" spans="52:52">
-      <c r="AZ193" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="194" spans="52:52">
-      <c r="AZ194" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="195" spans="52:52">
-      <c r="AZ195" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="196" spans="52:52">
-      <c r="AZ196" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="197" spans="52:52">
-      <c r="AZ197" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="198" spans="52:52">
-      <c r="AZ198" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="199" spans="52:52">
-      <c r="AZ199" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="200" spans="52:52">
-      <c r="AZ200" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="201" spans="52:52">
-      <c r="AZ201" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="202" spans="52:52">
-      <c r="AZ202" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="203" spans="52:52">
-      <c r="AZ203" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="204" spans="52:52">
-      <c r="AZ204" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="205" spans="52:52">
-      <c r="AZ205" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="206" spans="52:52">
-      <c r="AZ206" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="207" spans="52:52">
-      <c r="AZ207" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="208" spans="52:52">
-      <c r="AZ208" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="209" spans="52:52">
-      <c r="AZ209" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="210" spans="52:52">
-      <c r="AZ210" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="211" spans="52:52">
-      <c r="AZ211" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="212" spans="52:52">
-      <c r="AZ212" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="213" spans="52:52">
-      <c r="AZ213" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="214" spans="52:52">
-      <c r="AZ214" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="215" spans="52:52">
-      <c r="AZ215" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="216" spans="52:52">
-      <c r="AZ216" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="217" spans="52:52">
-      <c r="AZ217" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="218" spans="52:52">
-      <c r="AZ218" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="219" spans="52:52">
-      <c r="AZ219" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="220" spans="52:52">
-      <c r="AZ220" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="221" spans="52:52">
-      <c r="AZ221" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="222" spans="52:52">
-      <c r="AZ222" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="223" spans="52:52">
-      <c r="AZ223" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="224" spans="52:52">
-      <c r="AZ224" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="225" spans="52:52">
-      <c r="AZ225" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="226" spans="52:52">
-      <c r="AZ226" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="227" spans="52:52">
-      <c r="AZ227" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="228" spans="52:52">
-      <c r="AZ228" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="229" spans="52:52">
-      <c r="AZ229" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="230" spans="52:52">
-      <c r="AZ230" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="231" spans="52:52">
-      <c r="AZ231" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="232" spans="52:52">
-      <c r="AZ232" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="233" spans="52:52">
-      <c r="AZ233" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="234" spans="52:52">
-      <c r="AZ234" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="235" spans="52:52">
-      <c r="AZ235" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="236" spans="52:52">
-      <c r="AZ236" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="237" spans="52:52">
-      <c r="AZ237" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="238" spans="52:52">
-      <c r="AZ238" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="239" spans="52:52">
-      <c r="AZ239" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="240" spans="52:52">
-      <c r="AZ240" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="241" spans="52:52">
-      <c r="AZ241" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="242" spans="52:52">
-      <c r="AZ242" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="243" spans="52:52">
-      <c r="AZ243" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="244" spans="52:52">
-      <c r="AZ244" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="245" spans="52:52">
-      <c r="AZ245" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="246" spans="52:52">
-      <c r="AZ246" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="247" spans="52:52">
-      <c r="AZ247" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="248" spans="52:52">
-      <c r="AZ248" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="249" spans="52:52">
-      <c r="AZ249" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="250" spans="52:52">
-      <c r="AZ250" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="251" spans="52:52">
-      <c r="AZ251" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="252" spans="52:52">
-      <c r="AZ252" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="253" spans="52:52">
-      <c r="AZ253" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="254" spans="52:52">
-      <c r="AZ254" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="255" spans="52:52">
-      <c r="AZ255" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="256" spans="52:52">
-      <c r="AZ256" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="257" spans="52:52">
-      <c r="AZ257" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="258" spans="52:52">
-      <c r="AZ258" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="259" spans="52:52">
-      <c r="AZ259" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="260" spans="52:52">
-      <c r="AZ260" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="261" spans="52:52">
-      <c r="AZ261" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="262" spans="52:52">
-      <c r="AZ262" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="263" spans="52:52">
-      <c r="AZ263" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="264" spans="52:52">
-      <c r="AZ264" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="265" spans="52:52">
-      <c r="AZ265" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="266" spans="52:52">
-      <c r="AZ266" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="267" spans="52:52">
-      <c r="AZ267" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="268" spans="52:52">
-      <c r="AZ268" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="269" spans="52:52">
-      <c r="AZ269" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="270" spans="52:52">
-      <c r="AZ270" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="271" spans="52:52">
-      <c r="AZ271" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="272" spans="52:52">
-      <c r="AZ272" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="273" spans="52:52">
-      <c r="AZ273" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="274" spans="52:52">
-      <c r="AZ274" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="275" spans="52:52">
-      <c r="AZ275" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="276" spans="52:52">
-      <c r="AZ276" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="277" spans="52:52">
-      <c r="AZ277" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="278" spans="52:52">
-      <c r="AZ278" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="279" spans="52:52">
-      <c r="AZ279" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="280" spans="52:52">
-      <c r="AZ280" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="281" spans="52:52">
-      <c r="AZ281" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="282" spans="52:52">
-      <c r="AZ282" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="283" spans="52:52">
-      <c r="AZ283" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="284" spans="52:52">
-      <c r="AZ284" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="285" spans="52:52">
-      <c r="AZ285" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="286" spans="52:52">
-      <c r="AZ286" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="287" spans="52:52">
-      <c r="AZ287" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="288" spans="52:52">
-      <c r="AZ288" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="289" spans="52:52">
-      <c r="AZ289" t="s">
-        <v>706</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000037/metadata_template_ERC000037.xlsx
+++ b/templates/ERC000037/metadata_template_ERC000037.xlsx
@@ -17,20 +17,20 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="drainageclassification">'cv_sample'!$BE$1:$BE$6</definedName>
+    <definedName name="drainageclassification">'cv_sample'!$BF$1:$BF$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BA$1:$BA$294</definedName>
-    <definedName name="growthfacility">'cv_sample'!$S$1:$S$6</definedName>
-    <definedName name="growthhabit">'cv_sample'!$AW$1:$AW$4</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BB$1:$BB$294</definedName>
+    <definedName name="growthfacility">'cv_sample'!$T$1:$T$6</definedName>
+    <definedName name="growthhabit">'cv_sample'!$AX$1:$AX$4</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="samplecapturestatus">'cv_sample'!$AT$1:$AT$7</definedName>
-    <definedName name="samplehealthstate">'cv_sample'!$V$1:$V$2</definedName>
-    <definedName name="soiltype">'cv_sample'!$N$1:$N$32</definedName>
+    <definedName name="samplecapturestatus">'cv_sample'!$AU$1:$AU$7</definedName>
+    <definedName name="samplehealthstate">'cv_sample'!$W$1:$W$2</definedName>
+    <definedName name="soiltype">'cv_sample'!$O$1:$O$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="828">
   <si>
     <t>alias</t>
   </si>
@@ -854,6 +854,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4039,13 +4045,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CZ2"/>
+  <dimension ref="A1:DA2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104">
+    <row r="1" spans="1:105">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4062,7 +4068,7 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>281</v>
@@ -4086,7 +4092,7 @@
         <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>329</v>
@@ -4101,7 +4107,7 @@
         <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>344</v>
@@ -4110,7 +4116,7 @@
         <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>352</v>
@@ -4182,7 +4188,7 @@
         <v>396</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>406</v>
@@ -4191,7 +4197,7 @@
         <v>408</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AX1" s="1" t="s">
         <v>416</v>
@@ -4203,7 +4209,7 @@
         <v>420</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>716</v>
+        <v>422</v>
       </c>
       <c r="BB1" s="1" t="s">
         <v>718</v>
@@ -4215,7 +4221,7 @@
         <v>722</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>732</v>
@@ -4358,8 +4364,11 @@
       <c r="CZ1" s="1" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="2" spans="1:104" ht="150" customHeight="1">
+      <c r="DA1" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="2" spans="1:105" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4376,7 +4385,7 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>282</v>
@@ -4400,7 +4409,7 @@
         <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>330</v>
@@ -4415,7 +4424,7 @@
         <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>345</v>
@@ -4424,7 +4433,7 @@
         <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>353</v>
@@ -4496,7 +4505,7 @@
         <v>397</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="AU2" s="2" t="s">
         <v>407</v>
@@ -4505,7 +4514,7 @@
         <v>409</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="2" t="s">
         <v>417</v>
@@ -4517,7 +4526,7 @@
         <v>421</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>717</v>
+        <v>423</v>
       </c>
       <c r="BB2" s="2" t="s">
         <v>719</v>
@@ -4529,7 +4538,7 @@
         <v>723</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="BF2" s="2" t="s">
         <v>733</v>
@@ -4672,31 +4681,34 @@
       <c r="CZ2" s="2" t="s">
         <v>825</v>
       </c>
+      <c r="DA2" s="2" t="s">
+        <v>827</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
       <formula1>growthfacility</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
       <formula1>samplehealthstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
       <formula1>samplecapturestatus</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
       <formula1>growthhabit</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA3:BA101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB3:BB101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE3:BE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF101">
       <formula1>drainageclassification</formula1>
     </dataValidation>
   </dataValidations>
@@ -4706,1663 +4718,1663 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:BE294"/>
+  <dimension ref="G1:BF294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:57">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
-      <c r="N1" t="s">
-        <v>295</v>
-      </c>
-      <c r="S1" t="s">
-        <v>337</v>
-      </c>
-      <c r="V1" t="s">
-        <v>348</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>410</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>422</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="2" spans="6:57">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
-      <c r="N2" t="s">
-        <v>296</v>
-      </c>
-      <c r="S2" t="s">
-        <v>338</v>
-      </c>
-      <c r="V2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>399</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>411</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>423</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="3" spans="6:57">
-      <c r="F3" t="s">
+    <row r="1" spans="7:58">
+      <c r="G1" t="s">
         <v>276</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O1" t="s">
         <v>297</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T1" t="s">
         <v>339</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="W1" t="s">
+        <v>350</v>
+      </c>
+      <c r="AU1" t="s">
         <v>400</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX1" t="s">
         <v>412</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BB1" t="s">
         <v>424</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BF1" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="4" spans="6:57">
-      <c r="F4" t="s">
+    <row r="2" spans="7:58">
+      <c r="G2" t="s">
         <v>277</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O2" t="s">
         <v>298</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T2" t="s">
         <v>340</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="W2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AU2" t="s">
         <v>401</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX2" t="s">
         <v>413</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB2" t="s">
         <v>425</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF2" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="5" spans="6:57">
-      <c r="F5" t="s">
+    <row r="3" spans="7:58">
+      <c r="G3" t="s">
         <v>278</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O3" t="s">
         <v>299</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T3" t="s">
         <v>341</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AU3" t="s">
+        <v>402</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>414</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>426</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="4" spans="7:58">
+      <c r="G4" t="s">
+        <v>279</v>
+      </c>
+      <c r="O4" t="s">
+        <v>300</v>
+      </c>
+      <c r="T4" t="s">
+        <v>342</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>403</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>415</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>427</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="5" spans="7:58">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="O5" t="s">
+        <v>301</v>
+      </c>
+      <c r="T5" t="s">
+        <v>343</v>
+      </c>
+      <c r="AU5" t="s">
         <v>116</v>
       </c>
-      <c r="BA5" t="s">
-        <v>426</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="6" spans="6:57">
-      <c r="N6" t="s">
-        <v>300</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="BB5" t="s">
+        <v>428</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="6" spans="7:58">
+      <c r="O6" t="s">
+        <v>302</v>
+      </c>
+      <c r="T6" t="s">
         <v>116</v>
       </c>
-      <c r="AT6" t="s">
-        <v>402</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>427</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="7" spans="6:57">
-      <c r="N7" t="s">
-        <v>301</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>403</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="8" spans="6:57">
-      <c r="N8" t="s">
-        <v>302</v>
-      </c>
-      <c r="BA8" t="s">
+      <c r="AU6" t="s">
+        <v>404</v>
+      </c>
+      <c r="BB6" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="9" spans="6:57">
-      <c r="N9" t="s">
+      <c r="BF6" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="7" spans="7:58">
+      <c r="O7" t="s">
         <v>303</v>
       </c>
-      <c r="BA9" t="s">
+      <c r="AU7" t="s">
+        <v>405</v>
+      </c>
+      <c r="BB7" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="6:57">
-      <c r="N10" t="s">
+    <row r="8" spans="7:58">
+      <c r="O8" t="s">
         <v>304</v>
       </c>
-      <c r="BA10" t="s">
+      <c r="BB8" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="11" spans="6:57">
-      <c r="N11" t="s">
+    <row r="9" spans="7:58">
+      <c r="O9" t="s">
         <v>305</v>
       </c>
-      <c r="BA11" t="s">
+      <c r="BB9" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="12" spans="6:57">
-      <c r="N12" t="s">
+    <row r="10" spans="7:58">
+      <c r="O10" t="s">
         <v>306</v>
       </c>
-      <c r="BA12" t="s">
+      <c r="BB10" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="13" spans="6:57">
-      <c r="N13" t="s">
+    <row r="11" spans="7:58">
+      <c r="O11" t="s">
         <v>307</v>
       </c>
-      <c r="BA13" t="s">
+      <c r="BB11" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="14" spans="6:57">
-      <c r="N14" t="s">
+    <row r="12" spans="7:58">
+      <c r="O12" t="s">
         <v>308</v>
       </c>
-      <c r="BA14" t="s">
+      <c r="BB12" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="15" spans="6:57">
-      <c r="N15" t="s">
+    <row r="13" spans="7:58">
+      <c r="O13" t="s">
         <v>309</v>
       </c>
-      <c r="BA15" t="s">
+      <c r="BB13" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="16" spans="6:57">
-      <c r="N16" t="s">
+    <row r="14" spans="7:58">
+      <c r="O14" t="s">
         <v>310</v>
       </c>
-      <c r="BA16" t="s">
+      <c r="BB14" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="17" spans="14:53">
-      <c r="N17" t="s">
+    <row r="15" spans="7:58">
+      <c r="O15" t="s">
         <v>311</v>
       </c>
-      <c r="BA17" t="s">
+      <c r="BB15" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="18" spans="14:53">
-      <c r="N18" t="s">
+    <row r="16" spans="7:58">
+      <c r="O16" t="s">
         <v>312</v>
       </c>
-      <c r="BA18" t="s">
+      <c r="BB16" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="19" spans="14:53">
-      <c r="N19" t="s">
+    <row r="17" spans="15:54">
+      <c r="O17" t="s">
         <v>313</v>
       </c>
-      <c r="BA19" t="s">
+      <c r="BB17" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="20" spans="14:53">
-      <c r="N20" t="s">
+    <row r="18" spans="15:54">
+      <c r="O18" t="s">
         <v>314</v>
       </c>
-      <c r="BA20" t="s">
+      <c r="BB18" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="21" spans="14:53">
-      <c r="N21" t="s">
+    <row r="19" spans="15:54">
+      <c r="O19" t="s">
         <v>315</v>
       </c>
-      <c r="BA21" t="s">
+      <c r="BB19" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="22" spans="14:53">
-      <c r="N22" t="s">
+    <row r="20" spans="15:54">
+      <c r="O20" t="s">
         <v>316</v>
       </c>
-      <c r="BA22" t="s">
+      <c r="BB20" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="23" spans="14:53">
-      <c r="N23" t="s">
+    <row r="21" spans="15:54">
+      <c r="O21" t="s">
         <v>317</v>
       </c>
-      <c r="BA23" t="s">
+      <c r="BB21" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="24" spans="14:53">
-      <c r="N24" t="s">
+    <row r="22" spans="15:54">
+      <c r="O22" t="s">
         <v>318</v>
       </c>
-      <c r="BA24" t="s">
+      <c r="BB22" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="25" spans="14:53">
-      <c r="N25" t="s">
+    <row r="23" spans="15:54">
+      <c r="O23" t="s">
         <v>319</v>
       </c>
-      <c r="BA25" t="s">
+      <c r="BB23" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="26" spans="14:53">
-      <c r="N26" t="s">
+    <row r="24" spans="15:54">
+      <c r="O24" t="s">
         <v>320</v>
       </c>
-      <c r="BA26" t="s">
+      <c r="BB24" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="27" spans="14:53">
-      <c r="N27" t="s">
+    <row r="25" spans="15:54">
+      <c r="O25" t="s">
         <v>321</v>
       </c>
-      <c r="BA27" t="s">
+      <c r="BB25" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="28" spans="14:53">
-      <c r="N28" t="s">
+    <row r="26" spans="15:54">
+      <c r="O26" t="s">
         <v>322</v>
       </c>
-      <c r="BA28" t="s">
+      <c r="BB26" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="29" spans="14:53">
-      <c r="N29" t="s">
+    <row r="27" spans="15:54">
+      <c r="O27" t="s">
         <v>323</v>
       </c>
-      <c r="BA29" t="s">
+      <c r="BB27" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="30" spans="14:53">
-      <c r="N30" t="s">
+    <row r="28" spans="15:54">
+      <c r="O28" t="s">
         <v>324</v>
       </c>
-      <c r="BA30" t="s">
+      <c r="BB28" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="31" spans="14:53">
-      <c r="N31" t="s">
+    <row r="29" spans="15:54">
+      <c r="O29" t="s">
         <v>325</v>
       </c>
-      <c r="BA31" t="s">
+      <c r="BB29" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="32" spans="14:53">
-      <c r="N32" t="s">
+    <row r="30" spans="15:54">
+      <c r="O30" t="s">
         <v>326</v>
       </c>
-      <c r="BA32" t="s">
+      <c r="BB30" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="33" spans="53:53">
-      <c r="BA33" t="s">
+    <row r="31" spans="15:54">
+      <c r="O31" t="s">
+        <v>327</v>
+      </c>
+      <c r="BB31" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="34" spans="53:53">
-      <c r="BA34" t="s">
+    <row r="32" spans="15:54">
+      <c r="O32" t="s">
+        <v>328</v>
+      </c>
+      <c r="BB32" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="35" spans="53:53">
-      <c r="BA35" t="s">
+    <row r="33" spans="54:54">
+      <c r="BB33" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="36" spans="53:53">
-      <c r="BA36" t="s">
+    <row r="34" spans="54:54">
+      <c r="BB34" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="37" spans="53:53">
-      <c r="BA37" t="s">
+    <row r="35" spans="54:54">
+      <c r="BB35" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="38" spans="53:53">
-      <c r="BA38" t="s">
+    <row r="36" spans="54:54">
+      <c r="BB36" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="39" spans="53:53">
-      <c r="BA39" t="s">
+    <row r="37" spans="54:54">
+      <c r="BB37" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="40" spans="53:53">
-      <c r="BA40" t="s">
+    <row r="38" spans="54:54">
+      <c r="BB38" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="41" spans="53:53">
-      <c r="BA41" t="s">
+    <row r="39" spans="54:54">
+      <c r="BB39" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="42" spans="53:53">
-      <c r="BA42" t="s">
+    <row r="40" spans="54:54">
+      <c r="BB40" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="43" spans="53:53">
-      <c r="BA43" t="s">
+    <row r="41" spans="54:54">
+      <c r="BB41" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="44" spans="53:53">
-      <c r="BA44" t="s">
+    <row r="42" spans="54:54">
+      <c r="BB42" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="45" spans="53:53">
-      <c r="BA45" t="s">
+    <row r="43" spans="54:54">
+      <c r="BB43" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="46" spans="53:53">
-      <c r="BA46" t="s">
+    <row r="44" spans="54:54">
+      <c r="BB44" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="47" spans="53:53">
-      <c r="BA47" t="s">
+    <row r="45" spans="54:54">
+      <c r="BB45" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="48" spans="53:53">
-      <c r="BA48" t="s">
+    <row r="46" spans="54:54">
+      <c r="BB46" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="49" spans="53:53">
-      <c r="BA49" t="s">
+    <row r="47" spans="54:54">
+      <c r="BB47" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="50" spans="53:53">
-      <c r="BA50" t="s">
+    <row r="48" spans="54:54">
+      <c r="BB48" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="51" spans="53:53">
-      <c r="BA51" t="s">
+    <row r="49" spans="54:54">
+      <c r="BB49" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="52" spans="53:53">
-      <c r="BA52" t="s">
+    <row r="50" spans="54:54">
+      <c r="BB50" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="53" spans="53:53">
-      <c r="BA53" t="s">
+    <row r="51" spans="54:54">
+      <c r="BB51" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="54" spans="53:53">
-      <c r="BA54" t="s">
+    <row r="52" spans="54:54">
+      <c r="BB52" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="55" spans="53:53">
-      <c r="BA55" t="s">
+    <row r="53" spans="54:54">
+      <c r="BB53" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="56" spans="53:53">
-      <c r="BA56" t="s">
+    <row r="54" spans="54:54">
+      <c r="BB54" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="57" spans="53:53">
-      <c r="BA57" t="s">
+    <row r="55" spans="54:54">
+      <c r="BB55" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="58" spans="53:53">
-      <c r="BA58" t="s">
+    <row r="56" spans="54:54">
+      <c r="BB56" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="59" spans="53:53">
-      <c r="BA59" t="s">
+    <row r="57" spans="54:54">
+      <c r="BB57" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="60" spans="53:53">
-      <c r="BA60" t="s">
+    <row r="58" spans="54:54">
+      <c r="BB58" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="61" spans="53:53">
-      <c r="BA61" t="s">
+    <row r="59" spans="54:54">
+      <c r="BB59" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="62" spans="53:53">
-      <c r="BA62" t="s">
+    <row r="60" spans="54:54">
+      <c r="BB60" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="63" spans="53:53">
-      <c r="BA63" t="s">
+    <row r="61" spans="54:54">
+      <c r="BB61" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="64" spans="53:53">
-      <c r="BA64" t="s">
+    <row r="62" spans="54:54">
+      <c r="BB62" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="65" spans="53:53">
-      <c r="BA65" t="s">
+    <row r="63" spans="54:54">
+      <c r="BB63" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="66" spans="53:53">
-      <c r="BA66" t="s">
+    <row r="64" spans="54:54">
+      <c r="BB64" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="67" spans="53:53">
-      <c r="BA67" t="s">
+    <row r="65" spans="54:54">
+      <c r="BB65" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="68" spans="53:53">
-      <c r="BA68" t="s">
+    <row r="66" spans="54:54">
+      <c r="BB66" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="69" spans="53:53">
-      <c r="BA69" t="s">
+    <row r="67" spans="54:54">
+      <c r="BB67" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="70" spans="53:53">
-      <c r="BA70" t="s">
+    <row r="68" spans="54:54">
+      <c r="BB68" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="71" spans="53:53">
-      <c r="BA71" t="s">
+    <row r="69" spans="54:54">
+      <c r="BB69" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="72" spans="53:53">
-      <c r="BA72" t="s">
+    <row r="70" spans="54:54">
+      <c r="BB70" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="73" spans="53:53">
-      <c r="BA73" t="s">
+    <row r="71" spans="54:54">
+      <c r="BB71" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="74" spans="53:53">
-      <c r="BA74" t="s">
+    <row r="72" spans="54:54">
+      <c r="BB72" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="75" spans="53:53">
-      <c r="BA75" t="s">
+    <row r="73" spans="54:54">
+      <c r="BB73" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="76" spans="53:53">
-      <c r="BA76" t="s">
+    <row r="74" spans="54:54">
+      <c r="BB74" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="77" spans="53:53">
-      <c r="BA77" t="s">
+    <row r="75" spans="54:54">
+      <c r="BB75" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="78" spans="53:53">
-      <c r="BA78" t="s">
+    <row r="76" spans="54:54">
+      <c r="BB76" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="79" spans="53:53">
-      <c r="BA79" t="s">
+    <row r="77" spans="54:54">
+      <c r="BB77" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="80" spans="53:53">
-      <c r="BA80" t="s">
+    <row r="78" spans="54:54">
+      <c r="BB78" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="81" spans="53:53">
-      <c r="BA81" t="s">
+    <row r="79" spans="54:54">
+      <c r="BB79" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="82" spans="53:53">
-      <c r="BA82" t="s">
+    <row r="80" spans="54:54">
+      <c r="BB80" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="83" spans="53:53">
-      <c r="BA83" t="s">
+    <row r="81" spans="54:54">
+      <c r="BB81" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="84" spans="53:53">
-      <c r="BA84" t="s">
+    <row r="82" spans="54:54">
+      <c r="BB82" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="85" spans="53:53">
-      <c r="BA85" t="s">
+    <row r="83" spans="54:54">
+      <c r="BB83" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="86" spans="53:53">
-      <c r="BA86" t="s">
+    <row r="84" spans="54:54">
+      <c r="BB84" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="87" spans="53:53">
-      <c r="BA87" t="s">
+    <row r="85" spans="54:54">
+      <c r="BB85" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="88" spans="53:53">
-      <c r="BA88" t="s">
+    <row r="86" spans="54:54">
+      <c r="BB86" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="89" spans="53:53">
-      <c r="BA89" t="s">
+    <row r="87" spans="54:54">
+      <c r="BB87" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="90" spans="53:53">
-      <c r="BA90" t="s">
+    <row r="88" spans="54:54">
+      <c r="BB88" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="91" spans="53:53">
-      <c r="BA91" t="s">
+    <row r="89" spans="54:54">
+      <c r="BB89" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="92" spans="53:53">
-      <c r="BA92" t="s">
+    <row r="90" spans="54:54">
+      <c r="BB90" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="93" spans="53:53">
-      <c r="BA93" t="s">
+    <row r="91" spans="54:54">
+      <c r="BB91" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="94" spans="53:53">
-      <c r="BA94" t="s">
+    <row r="92" spans="54:54">
+      <c r="BB92" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="95" spans="53:53">
-      <c r="BA95" t="s">
+    <row r="93" spans="54:54">
+      <c r="BB93" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="96" spans="53:53">
-      <c r="BA96" t="s">
+    <row r="94" spans="54:54">
+      <c r="BB94" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="97" spans="53:53">
-      <c r="BA97" t="s">
+    <row r="95" spans="54:54">
+      <c r="BB95" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="98" spans="53:53">
-      <c r="BA98" t="s">
+    <row r="96" spans="54:54">
+      <c r="BB96" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="99" spans="53:53">
-      <c r="BA99" t="s">
+    <row r="97" spans="54:54">
+      <c r="BB97" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="100" spans="53:53">
-      <c r="BA100" t="s">
+    <row r="98" spans="54:54">
+      <c r="BB98" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="101" spans="53:53">
-      <c r="BA101" t="s">
+    <row r="99" spans="54:54">
+      <c r="BB99" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="102" spans="53:53">
-      <c r="BA102" t="s">
+    <row r="100" spans="54:54">
+      <c r="BB100" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="103" spans="53:53">
-      <c r="BA103" t="s">
+    <row r="101" spans="54:54">
+      <c r="BB101" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="104" spans="53:53">
-      <c r="BA104" t="s">
+    <row r="102" spans="54:54">
+      <c r="BB102" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="105" spans="53:53">
-      <c r="BA105" t="s">
+    <row r="103" spans="54:54">
+      <c r="BB103" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="106" spans="53:53">
-      <c r="BA106" t="s">
+    <row r="104" spans="54:54">
+      <c r="BB104" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="107" spans="53:53">
-      <c r="BA107" t="s">
+    <row r="105" spans="54:54">
+      <c r="BB105" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="108" spans="53:53">
-      <c r="BA108" t="s">
+    <row r="106" spans="54:54">
+      <c r="BB106" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="109" spans="53:53">
-      <c r="BA109" t="s">
+    <row r="107" spans="54:54">
+      <c r="BB107" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="110" spans="53:53">
-      <c r="BA110" t="s">
+    <row r="108" spans="54:54">
+      <c r="BB108" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="111" spans="53:53">
-      <c r="BA111" t="s">
+    <row r="109" spans="54:54">
+      <c r="BB109" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="112" spans="53:53">
-      <c r="BA112" t="s">
+    <row r="110" spans="54:54">
+      <c r="BB110" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="113" spans="53:53">
-      <c r="BA113" t="s">
+    <row r="111" spans="54:54">
+      <c r="BB111" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="114" spans="53:53">
-      <c r="BA114" t="s">
+    <row r="112" spans="54:54">
+      <c r="BB112" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="115" spans="53:53">
-      <c r="BA115" t="s">
+    <row r="113" spans="54:54">
+      <c r="BB113" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="116" spans="53:53">
-      <c r="BA116" t="s">
+    <row r="114" spans="54:54">
+      <c r="BB114" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="117" spans="53:53">
-      <c r="BA117" t="s">
+    <row r="115" spans="54:54">
+      <c r="BB115" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="118" spans="53:53">
-      <c r="BA118" t="s">
+    <row r="116" spans="54:54">
+      <c r="BB116" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="119" spans="53:53">
-      <c r="BA119" t="s">
+    <row r="117" spans="54:54">
+      <c r="BB117" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="120" spans="53:53">
-      <c r="BA120" t="s">
+    <row r="118" spans="54:54">
+      <c r="BB118" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="121" spans="53:53">
-      <c r="BA121" t="s">
+    <row r="119" spans="54:54">
+      <c r="BB119" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="122" spans="53:53">
-      <c r="BA122" t="s">
+    <row r="120" spans="54:54">
+      <c r="BB120" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="123" spans="53:53">
-      <c r="BA123" t="s">
+    <row r="121" spans="54:54">
+      <c r="BB121" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="124" spans="53:53">
-      <c r="BA124" t="s">
+    <row r="122" spans="54:54">
+      <c r="BB122" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="125" spans="53:53">
-      <c r="BA125" t="s">
+    <row r="123" spans="54:54">
+      <c r="BB123" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="126" spans="53:53">
-      <c r="BA126" t="s">
+    <row r="124" spans="54:54">
+      <c r="BB124" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="127" spans="53:53">
-      <c r="BA127" t="s">
+    <row r="125" spans="54:54">
+      <c r="BB125" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="128" spans="53:53">
-      <c r="BA128" t="s">
+    <row r="126" spans="54:54">
+      <c r="BB126" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="129" spans="53:53">
-      <c r="BA129" t="s">
+    <row r="127" spans="54:54">
+      <c r="BB127" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="130" spans="53:53">
-      <c r="BA130" t="s">
+    <row r="128" spans="54:54">
+      <c r="BB128" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="131" spans="53:53">
-      <c r="BA131" t="s">
+    <row r="129" spans="54:54">
+      <c r="BB129" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="132" spans="53:53">
-      <c r="BA132" t="s">
+    <row r="130" spans="54:54">
+      <c r="BB130" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="133" spans="53:53">
-      <c r="BA133" t="s">
+    <row r="131" spans="54:54">
+      <c r="BB131" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="134" spans="53:53">
-      <c r="BA134" t="s">
+    <row r="132" spans="54:54">
+      <c r="BB132" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="135" spans="53:53">
-      <c r="BA135" t="s">
+    <row r="133" spans="54:54">
+      <c r="BB133" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="136" spans="53:53">
-      <c r="BA136" t="s">
+    <row r="134" spans="54:54">
+      <c r="BB134" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="137" spans="53:53">
-      <c r="BA137" t="s">
+    <row r="135" spans="54:54">
+      <c r="BB135" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="138" spans="53:53">
-      <c r="BA138" t="s">
+    <row r="136" spans="54:54">
+      <c r="BB136" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="139" spans="53:53">
-      <c r="BA139" t="s">
+    <row r="137" spans="54:54">
+      <c r="BB137" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="140" spans="53:53">
-      <c r="BA140" t="s">
+    <row r="138" spans="54:54">
+      <c r="BB138" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="141" spans="53:53">
-      <c r="BA141" t="s">
+    <row r="139" spans="54:54">
+      <c r="BB139" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="142" spans="53:53">
-      <c r="BA142" t="s">
+    <row r="140" spans="54:54">
+      <c r="BB140" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="143" spans="53:53">
-      <c r="BA143" t="s">
+    <row r="141" spans="54:54">
+      <c r="BB141" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="144" spans="53:53">
-      <c r="BA144" t="s">
+    <row r="142" spans="54:54">
+      <c r="BB142" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="145" spans="53:53">
-      <c r="BA145" t="s">
+    <row r="143" spans="54:54">
+      <c r="BB143" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="146" spans="53:53">
-      <c r="BA146" t="s">
+    <row r="144" spans="54:54">
+      <c r="BB144" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="147" spans="53:53">
-      <c r="BA147" t="s">
+    <row r="145" spans="54:54">
+      <c r="BB145" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="148" spans="53:53">
-      <c r="BA148" t="s">
+    <row r="146" spans="54:54">
+      <c r="BB146" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="149" spans="53:53">
-      <c r="BA149" t="s">
+    <row r="147" spans="54:54">
+      <c r="BB147" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="150" spans="53:53">
-      <c r="BA150" t="s">
+    <row r="148" spans="54:54">
+      <c r="BB148" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="151" spans="53:53">
-      <c r="BA151" t="s">
+    <row r="149" spans="54:54">
+      <c r="BB149" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="152" spans="53:53">
-      <c r="BA152" t="s">
+    <row r="150" spans="54:54">
+      <c r="BB150" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="153" spans="53:53">
-      <c r="BA153" t="s">
+    <row r="151" spans="54:54">
+      <c r="BB151" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="154" spans="53:53">
-      <c r="BA154" t="s">
+    <row r="152" spans="54:54">
+      <c r="BB152" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="155" spans="53:53">
-      <c r="BA155" t="s">
+    <row r="153" spans="54:54">
+      <c r="BB153" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="156" spans="53:53">
-      <c r="BA156" t="s">
+    <row r="154" spans="54:54">
+      <c r="BB154" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="157" spans="53:53">
-      <c r="BA157" t="s">
+    <row r="155" spans="54:54">
+      <c r="BB155" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="158" spans="53:53">
-      <c r="BA158" t="s">
+    <row r="156" spans="54:54">
+      <c r="BB156" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="159" spans="53:53">
-      <c r="BA159" t="s">
+    <row r="157" spans="54:54">
+      <c r="BB157" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="160" spans="53:53">
-      <c r="BA160" t="s">
+    <row r="158" spans="54:54">
+      <c r="BB158" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="161" spans="53:53">
-      <c r="BA161" t="s">
+    <row r="159" spans="54:54">
+      <c r="BB159" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="162" spans="53:53">
-      <c r="BA162" t="s">
+    <row r="160" spans="54:54">
+      <c r="BB160" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="163" spans="53:53">
-      <c r="BA163" t="s">
+    <row r="161" spans="54:54">
+      <c r="BB161" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="164" spans="53:53">
-      <c r="BA164" t="s">
+    <row r="162" spans="54:54">
+      <c r="BB162" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="165" spans="53:53">
-      <c r="BA165" t="s">
+    <row r="163" spans="54:54">
+      <c r="BB163" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="166" spans="53:53">
-      <c r="BA166" t="s">
+    <row r="164" spans="54:54">
+      <c r="BB164" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="167" spans="53:53">
-      <c r="BA167" t="s">
+    <row r="165" spans="54:54">
+      <c r="BB165" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="168" spans="53:53">
-      <c r="BA168" t="s">
+    <row r="166" spans="54:54">
+      <c r="BB166" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="169" spans="53:53">
-      <c r="BA169" t="s">
+    <row r="167" spans="54:54">
+      <c r="BB167" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="170" spans="53:53">
-      <c r="BA170" t="s">
+    <row r="168" spans="54:54">
+      <c r="BB168" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="171" spans="53:53">
-      <c r="BA171" t="s">
+    <row r="169" spans="54:54">
+      <c r="BB169" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="172" spans="53:53">
-      <c r="BA172" t="s">
+    <row r="170" spans="54:54">
+      <c r="BB170" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="53:53">
-      <c r="BA173" t="s">
+    <row r="171" spans="54:54">
+      <c r="BB171" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="174" spans="53:53">
-      <c r="BA174" t="s">
+    <row r="172" spans="54:54">
+      <c r="BB172" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="175" spans="53:53">
-      <c r="BA175" t="s">
+    <row r="173" spans="54:54">
+      <c r="BB173" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="176" spans="53:53">
-      <c r="BA176" t="s">
+    <row r="174" spans="54:54">
+      <c r="BB174" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="177" spans="53:53">
-      <c r="BA177" t="s">
+    <row r="175" spans="54:54">
+      <c r="BB175" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="178" spans="53:53">
-      <c r="BA178" t="s">
+    <row r="176" spans="54:54">
+      <c r="BB176" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="179" spans="53:53">
-      <c r="BA179" t="s">
+    <row r="177" spans="54:54">
+      <c r="BB177" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="180" spans="53:53">
-      <c r="BA180" t="s">
+    <row r="178" spans="54:54">
+      <c r="BB178" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="181" spans="53:53">
-      <c r="BA181" t="s">
+    <row r="179" spans="54:54">
+      <c r="BB179" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="182" spans="53:53">
-      <c r="BA182" t="s">
+    <row r="180" spans="54:54">
+      <c r="BB180" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="183" spans="53:53">
-      <c r="BA183" t="s">
+    <row r="181" spans="54:54">
+      <c r="BB181" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="184" spans="53:53">
-      <c r="BA184" t="s">
+    <row r="182" spans="54:54">
+      <c r="BB182" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="185" spans="53:53">
-      <c r="BA185" t="s">
+    <row r="183" spans="54:54">
+      <c r="BB183" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="186" spans="53:53">
-      <c r="BA186" t="s">
+    <row r="184" spans="54:54">
+      <c r="BB184" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="187" spans="53:53">
-      <c r="BA187" t="s">
+    <row r="185" spans="54:54">
+      <c r="BB185" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="188" spans="53:53">
-      <c r="BA188" t="s">
+    <row r="186" spans="54:54">
+      <c r="BB186" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="189" spans="53:53">
-      <c r="BA189" t="s">
+    <row r="187" spans="54:54">
+      <c r="BB187" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="190" spans="53:53">
-      <c r="BA190" t="s">
+    <row r="188" spans="54:54">
+      <c r="BB188" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="191" spans="53:53">
-      <c r="BA191" t="s">
+    <row r="189" spans="54:54">
+      <c r="BB189" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="192" spans="53:53">
-      <c r="BA192" t="s">
+    <row r="190" spans="54:54">
+      <c r="BB190" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="193" spans="53:53">
-      <c r="BA193" t="s">
+    <row r="191" spans="54:54">
+      <c r="BB191" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="194" spans="53:53">
-      <c r="BA194" t="s">
+    <row r="192" spans="54:54">
+      <c r="BB192" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="195" spans="53:53">
-      <c r="BA195" t="s">
+    <row r="193" spans="54:54">
+      <c r="BB193" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="196" spans="53:53">
-      <c r="BA196" t="s">
+    <row r="194" spans="54:54">
+      <c r="BB194" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="197" spans="53:53">
-      <c r="BA197" t="s">
+    <row r="195" spans="54:54">
+      <c r="BB195" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="198" spans="53:53">
-      <c r="BA198" t="s">
+    <row r="196" spans="54:54">
+      <c r="BB196" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="199" spans="53:53">
-      <c r="BA199" t="s">
+    <row r="197" spans="54:54">
+      <c r="BB197" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="200" spans="53:53">
-      <c r="BA200" t="s">
+    <row r="198" spans="54:54">
+      <c r="BB198" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="201" spans="53:53">
-      <c r="BA201" t="s">
+    <row r="199" spans="54:54">
+      <c r="BB199" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="202" spans="53:53">
-      <c r="BA202" t="s">
+    <row r="200" spans="54:54">
+      <c r="BB200" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="203" spans="53:53">
-      <c r="BA203" t="s">
+    <row r="201" spans="54:54">
+      <c r="BB201" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="204" spans="53:53">
-      <c r="BA204" t="s">
+    <row r="202" spans="54:54">
+      <c r="BB202" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="205" spans="53:53">
-      <c r="BA205" t="s">
+    <row r="203" spans="54:54">
+      <c r="BB203" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="206" spans="53:53">
-      <c r="BA206" t="s">
+    <row r="204" spans="54:54">
+      <c r="BB204" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="207" spans="53:53">
-      <c r="BA207" t="s">
+    <row r="205" spans="54:54">
+      <c r="BB205" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="208" spans="53:53">
-      <c r="BA208" t="s">
+    <row r="206" spans="54:54">
+      <c r="BB206" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="209" spans="53:53">
-      <c r="BA209" t="s">
+    <row r="207" spans="54:54">
+      <c r="BB207" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="210" spans="53:53">
-      <c r="BA210" t="s">
+    <row r="208" spans="54:54">
+      <c r="BB208" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="211" spans="53:53">
-      <c r="BA211" t="s">
+    <row r="209" spans="54:54">
+      <c r="BB209" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="212" spans="53:53">
-      <c r="BA212" t="s">
+    <row r="210" spans="54:54">
+      <c r="BB210" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="213" spans="53:53">
-      <c r="BA213" t="s">
+    <row r="211" spans="54:54">
+      <c r="BB211" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="214" spans="53:53">
-      <c r="BA214" t="s">
+    <row r="212" spans="54:54">
+      <c r="BB212" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="215" spans="53:53">
-      <c r="BA215" t="s">
+    <row r="213" spans="54:54">
+      <c r="BB213" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="216" spans="53:53">
-      <c r="BA216" t="s">
+    <row r="214" spans="54:54">
+      <c r="BB214" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="217" spans="53:53">
-      <c r="BA217" t="s">
+    <row r="215" spans="54:54">
+      <c r="BB215" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="218" spans="53:53">
-      <c r="BA218" t="s">
+    <row r="216" spans="54:54">
+      <c r="BB216" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="219" spans="53:53">
-      <c r="BA219" t="s">
+    <row r="217" spans="54:54">
+      <c r="BB217" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="220" spans="53:53">
-      <c r="BA220" t="s">
+    <row r="218" spans="54:54">
+      <c r="BB218" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="221" spans="53:53">
-      <c r="BA221" t="s">
+    <row r="219" spans="54:54">
+      <c r="BB219" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="222" spans="53:53">
-      <c r="BA222" t="s">
+    <row r="220" spans="54:54">
+      <c r="BB220" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="223" spans="53:53">
-      <c r="BA223" t="s">
+    <row r="221" spans="54:54">
+      <c r="BB221" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="224" spans="53:53">
-      <c r="BA224" t="s">
+    <row r="222" spans="54:54">
+      <c r="BB222" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="225" spans="53:53">
-      <c r="BA225" t="s">
+    <row r="223" spans="54:54">
+      <c r="BB223" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="226" spans="53:53">
-      <c r="BA226" t="s">
+    <row r="224" spans="54:54">
+      <c r="BB224" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="227" spans="53:53">
-      <c r="BA227" t="s">
+    <row r="225" spans="54:54">
+      <c r="BB225" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="228" spans="53:53">
-      <c r="BA228" t="s">
+    <row r="226" spans="54:54">
+      <c r="BB226" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="229" spans="53:53">
-      <c r="BA229" t="s">
+    <row r="227" spans="54:54">
+      <c r="BB227" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="230" spans="53:53">
-      <c r="BA230" t="s">
+    <row r="228" spans="54:54">
+      <c r="BB228" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="231" spans="53:53">
-      <c r="BA231" t="s">
+    <row r="229" spans="54:54">
+      <c r="BB229" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="232" spans="53:53">
-      <c r="BA232" t="s">
+    <row r="230" spans="54:54">
+      <c r="BB230" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="233" spans="53:53">
-      <c r="BA233" t="s">
+    <row r="231" spans="54:54">
+      <c r="BB231" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="234" spans="53:53">
-      <c r="BA234" t="s">
+    <row r="232" spans="54:54">
+      <c r="BB232" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="235" spans="53:53">
-      <c r="BA235" t="s">
+    <row r="233" spans="54:54">
+      <c r="BB233" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="236" spans="53:53">
-      <c r="BA236" t="s">
+    <row r="234" spans="54:54">
+      <c r="BB234" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="237" spans="53:53">
-      <c r="BA237" t="s">
+    <row r="235" spans="54:54">
+      <c r="BB235" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="238" spans="53:53">
-      <c r="BA238" t="s">
+    <row r="236" spans="54:54">
+      <c r="BB236" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="239" spans="53:53">
-      <c r="BA239" t="s">
+    <row r="237" spans="54:54">
+      <c r="BB237" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="240" spans="53:53">
-      <c r="BA240" t="s">
+    <row r="238" spans="54:54">
+      <c r="BB238" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="241" spans="53:53">
-      <c r="BA241" t="s">
+    <row r="239" spans="54:54">
+      <c r="BB239" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="242" spans="53:53">
-      <c r="BA242" t="s">
+    <row r="240" spans="54:54">
+      <c r="BB240" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="243" spans="53:53">
-      <c r="BA243" t="s">
+    <row r="241" spans="54:54">
+      <c r="BB241" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="244" spans="53:53">
-      <c r="BA244" t="s">
+    <row r="242" spans="54:54">
+      <c r="BB242" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="245" spans="53:53">
-      <c r="BA245" t="s">
+    <row r="243" spans="54:54">
+      <c r="BB243" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="246" spans="53:53">
-      <c r="BA246" t="s">
+    <row r="244" spans="54:54">
+      <c r="BB244" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="247" spans="53:53">
-      <c r="BA247" t="s">
+    <row r="245" spans="54:54">
+      <c r="BB245" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="248" spans="53:53">
-      <c r="BA248" t="s">
+    <row r="246" spans="54:54">
+      <c r="BB246" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="249" spans="53:53">
-      <c r="BA249" t="s">
+    <row r="247" spans="54:54">
+      <c r="BB247" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="250" spans="53:53">
-      <c r="BA250" t="s">
+    <row r="248" spans="54:54">
+      <c r="BB248" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="251" spans="53:53">
-      <c r="BA251" t="s">
+    <row r="249" spans="54:54">
+      <c r="BB249" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="252" spans="53:53">
-      <c r="BA252" t="s">
+    <row r="250" spans="54:54">
+      <c r="BB250" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="253" spans="53:53">
-      <c r="BA253" t="s">
+    <row r="251" spans="54:54">
+      <c r="BB251" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="254" spans="53:53">
-      <c r="BA254" t="s">
+    <row r="252" spans="54:54">
+      <c r="BB252" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="255" spans="53:53">
-      <c r="BA255" t="s">
+    <row r="253" spans="54:54">
+      <c r="BB253" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="256" spans="53:53">
-      <c r="BA256" t="s">
+    <row r="254" spans="54:54">
+      <c r="BB254" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="257" spans="53:53">
-      <c r="BA257" t="s">
+    <row r="255" spans="54:54">
+      <c r="BB255" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="258" spans="53:53">
-      <c r="BA258" t="s">
+    <row r="256" spans="54:54">
+      <c r="BB256" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="259" spans="53:53">
-      <c r="BA259" t="s">
+    <row r="257" spans="54:54">
+      <c r="BB257" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="260" spans="53:53">
-      <c r="BA260" t="s">
+    <row r="258" spans="54:54">
+      <c r="BB258" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="261" spans="53:53">
-      <c r="BA261" t="s">
+    <row r="259" spans="54:54">
+      <c r="BB259" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="262" spans="53:53">
-      <c r="BA262" t="s">
+    <row r="260" spans="54:54">
+      <c r="BB260" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="263" spans="53:53">
-      <c r="BA263" t="s">
+    <row r="261" spans="54:54">
+      <c r="BB261" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="264" spans="53:53">
-      <c r="BA264" t="s">
+    <row r="262" spans="54:54">
+      <c r="BB262" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="265" spans="53:53">
-      <c r="BA265" t="s">
+    <row r="263" spans="54:54">
+      <c r="BB263" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="266" spans="53:53">
-      <c r="BA266" t="s">
+    <row r="264" spans="54:54">
+      <c r="BB264" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="267" spans="53:53">
-      <c r="BA267" t="s">
+    <row r="265" spans="54:54">
+      <c r="BB265" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="268" spans="53:53">
-      <c r="BA268" t="s">
+    <row r="266" spans="54:54">
+      <c r="BB266" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="269" spans="53:53">
-      <c r="BA269" t="s">
+    <row r="267" spans="54:54">
+      <c r="BB267" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="270" spans="53:53">
-      <c r="BA270" t="s">
+    <row r="268" spans="54:54">
+      <c r="BB268" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="271" spans="53:53">
-      <c r="BA271" t="s">
+    <row r="269" spans="54:54">
+      <c r="BB269" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="272" spans="53:53">
-      <c r="BA272" t="s">
+    <row r="270" spans="54:54">
+      <c r="BB270" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="273" spans="53:53">
-      <c r="BA273" t="s">
+    <row r="271" spans="54:54">
+      <c r="BB271" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="274" spans="53:53">
-      <c r="BA274" t="s">
+    <row r="272" spans="54:54">
+      <c r="BB272" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="275" spans="53:53">
-      <c r="BA275" t="s">
+    <row r="273" spans="54:54">
+      <c r="BB273" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="276" spans="53:53">
-      <c r="BA276" t="s">
+    <row r="274" spans="54:54">
+      <c r="BB274" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="277" spans="53:53">
-      <c r="BA277" t="s">
+    <row r="275" spans="54:54">
+      <c r="BB275" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="278" spans="53:53">
-      <c r="BA278" t="s">
+    <row r="276" spans="54:54">
+      <c r="BB276" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="279" spans="53:53">
-      <c r="BA279" t="s">
+    <row r="277" spans="54:54">
+      <c r="BB277" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="280" spans="53:53">
-      <c r="BA280" t="s">
+    <row r="278" spans="54:54">
+      <c r="BB278" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="281" spans="53:53">
-      <c r="BA281" t="s">
+    <row r="279" spans="54:54">
+      <c r="BB279" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="282" spans="53:53">
-      <c r="BA282" t="s">
+    <row r="280" spans="54:54">
+      <c r="BB280" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="283" spans="53:53">
-      <c r="BA283" t="s">
+    <row r="281" spans="54:54">
+      <c r="BB281" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="284" spans="53:53">
-      <c r="BA284" t="s">
+    <row r="282" spans="54:54">
+      <c r="BB282" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="285" spans="53:53">
-      <c r="BA285" t="s">
+    <row r="283" spans="54:54">
+      <c r="BB283" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="286" spans="53:53">
-      <c r="BA286" t="s">
+    <row r="284" spans="54:54">
+      <c r="BB284" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="287" spans="53:53">
-      <c r="BA287" t="s">
+    <row r="285" spans="54:54">
+      <c r="BB285" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="288" spans="53:53">
-      <c r="BA288" t="s">
+    <row r="286" spans="54:54">
+      <c r="BB286" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="289" spans="53:53">
-      <c r="BA289" t="s">
+    <row r="287" spans="54:54">
+      <c r="BB287" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="290" spans="53:53">
-      <c r="BA290" t="s">
+    <row r="288" spans="54:54">
+      <c r="BB288" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="291" spans="53:53">
-      <c r="BA291" t="s">
+    <row r="289" spans="54:54">
+      <c r="BB289" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="292" spans="53:53">
-      <c r="BA292" t="s">
+    <row r="290" spans="54:54">
+      <c r="BB290" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="293" spans="53:53">
-      <c r="BA293" t="s">
+    <row r="291" spans="54:54">
+      <c r="BB291" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="294" spans="53:53">
-      <c r="BA294" t="s">
+    <row r="292" spans="54:54">
+      <c r="BB292" t="s">
         <v>715</v>
+      </c>
+    </row>
+    <row r="293" spans="54:54">
+      <c r="BB293" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="294" spans="54:54">
+      <c r="BB294" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000037/metadata_template_ERC000037.xlsx
+++ b/templates/ERC000037/metadata_template_ERC000037.xlsx
@@ -19,15 +19,15 @@
   <definedNames>
     <definedName name="drainageclassification">'cv_sample'!$BF$1:$BF$6</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BB$1:$BB$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BB$1:$BB$294</definedName>
     <definedName name="growthfacility">'cv_sample'!$T$1:$T$6</definedName>
     <definedName name="growthhabit">'cv_sample'!$AX$1:$AX$4</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="samplecapturestatus">'cv_sample'!$AU$1:$AU$7</definedName>
     <definedName name="samplehealthstate">'cv_sample'!$W$1:$W$2</definedName>
     <definedName name="soiltype">'cv_sample'!$O$1:$O$32</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="828">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1519,9 +1525,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1540,6 +1543,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1741,6 +1747,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1750,9 +1759,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1792,7 +1798,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1861,6 +1867,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1936,6 +1945,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1957,6 +1969,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2002,6 +2017,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2014,6 +2032,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2023,9 +2044,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2050,6 +2068,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2110,10 +2131,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3027,10 +3048,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3071,10 +3092,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3101,7 +3122,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3118,7 +3139,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3135,7 +3156,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3152,7 +3173,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3169,7 +3190,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3186,7 +3207,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3203,7 +3224,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3220,7 +3241,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3237,7 +3258,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3254,7 +3275,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3268,7 +3289,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3282,7 +3303,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3296,7 +3317,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3310,7 +3331,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3324,7 +3345,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3338,7 +3359,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3352,7 +3373,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3366,7 +3387,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3376,8 +3397,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3388,7 +3412,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3399,7 +3423,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3410,7 +3434,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3421,7 +3445,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3432,7 +3456,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3443,7 +3467,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3454,7 +3478,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3465,7 +3489,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3476,7 +3500,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3487,7 +3511,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3498,7 +3522,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3509,7 +3533,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3520,7 +3544,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3528,7 +3552,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3536,7 +3560,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3544,7 +3568,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3552,7 +3576,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3560,7 +3584,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3568,7 +3592,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3576,7 +3600,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3584,7 +3608,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3592,7 +3616,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3600,236 +3624,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3851,27 +3880,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3891,122 +3920,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4030,630 +4059,630 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
     </row>
     <row r="2" spans="1:105" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -4689,1638 +4718,1663 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:BF289"/>
+  <dimension ref="G1:BF294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:58">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="T1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AU1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AX1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BB1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="BF1" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2" spans="7:58">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="W2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AU2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AX2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BB2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="BF2" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="7:58">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="T3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AU3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AX3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="BB3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="BF3" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="7:58">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="T4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AU4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AX4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BB4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="BF4" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="7:58">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="T5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AU5" t="s">
         <v>116</v>
       </c>
       <c r="BB5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="BF5" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="7:58">
       <c r="O6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="T6" t="s">
         <v>116</v>
       </c>
       <c r="AU6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BB6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BF6" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="7:58">
       <c r="O7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AU7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BB7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="7:58">
       <c r="O8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BB8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="7:58">
       <c r="O9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="BB9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="7:58">
       <c r="O10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="BB10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="7:58">
       <c r="O11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="BB11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="7:58">
       <c r="O12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="BB12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="7:58">
       <c r="O13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="BB13" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="7:58">
       <c r="O14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="BB14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="7:58">
       <c r="O15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="BB15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="7:58">
       <c r="O16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="BB16" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="15:54">
       <c r="O17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="BB17" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" spans="15:54">
       <c r="O18" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="BB18" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="15:54">
       <c r="O19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="BB19" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="15:54">
       <c r="O20" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="BB20" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="15:54">
       <c r="O21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="BB21" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="15:54">
       <c r="O22" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="BB22" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="15:54">
       <c r="O23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="BB23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="15:54">
       <c r="O24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="BB24" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="15:54">
       <c r="O25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="BB25" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="15:54">
       <c r="O26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BB26" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="27" spans="15:54">
       <c r="O27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BB27" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="15:54">
       <c r="O28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BB28" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" spans="15:54">
       <c r="O29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BB29" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" spans="15:54">
       <c r="O30" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BB30" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="15:54">
       <c r="O31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BB31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="15:54">
       <c r="O32" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BB32" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="54:54">
       <c r="BB33" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="54:54">
       <c r="BB34" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="35" spans="54:54">
       <c r="BB35" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="54:54">
       <c r="BB36" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="54:54">
       <c r="BB37" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="54:54">
       <c r="BB38" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="54:54">
       <c r="BB39" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40" spans="54:54">
       <c r="BB40" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="54:54">
       <c r="BB41" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="42" spans="54:54">
       <c r="BB42" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="43" spans="54:54">
       <c r="BB43" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" spans="54:54">
       <c r="BB44" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="54:54">
       <c r="BB45" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="46" spans="54:54">
       <c r="BB46" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" spans="54:54">
       <c r="BB47" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="48" spans="54:54">
       <c r="BB48" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" spans="54:54">
       <c r="BB49" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" spans="54:54">
       <c r="BB50" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="54:54">
       <c r="BB51" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="52" spans="54:54">
       <c r="BB52" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="53" spans="54:54">
       <c r="BB53" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="54" spans="54:54">
       <c r="BB54" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="55" spans="54:54">
       <c r="BB55" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="56" spans="54:54">
       <c r="BB56" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" spans="54:54">
       <c r="BB57" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58" spans="54:54">
       <c r="BB58" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="54:54">
       <c r="BB59" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="60" spans="54:54">
       <c r="BB60" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="54:54">
       <c r="BB61" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="62" spans="54:54">
       <c r="BB62" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="63" spans="54:54">
       <c r="BB63" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64" spans="54:54">
       <c r="BB64" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65" spans="54:54">
       <c r="BB65" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="66" spans="54:54">
       <c r="BB66" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="67" spans="54:54">
       <c r="BB67" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="68" spans="54:54">
       <c r="BB68" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="69" spans="54:54">
       <c r="BB69" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="70" spans="54:54">
       <c r="BB70" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="71" spans="54:54">
       <c r="BB71" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="72" spans="54:54">
       <c r="BB72" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="73" spans="54:54">
       <c r="BB73" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="74" spans="54:54">
       <c r="BB74" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="75" spans="54:54">
       <c r="BB75" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="76" spans="54:54">
       <c r="BB76" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="54:54">
       <c r="BB77" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="54:54">
       <c r="BB78" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="79" spans="54:54">
       <c r="BB79" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="80" spans="54:54">
       <c r="BB80" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="81" spans="54:54">
       <c r="BB81" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="54:54">
       <c r="BB82" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="83" spans="54:54">
       <c r="BB83" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="84" spans="54:54">
       <c r="BB84" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="85" spans="54:54">
       <c r="BB85" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="86" spans="54:54">
       <c r="BB86" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="87" spans="54:54">
       <c r="BB87" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="88" spans="54:54">
       <c r="BB88" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="89" spans="54:54">
       <c r="BB89" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="90" spans="54:54">
       <c r="BB90" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="91" spans="54:54">
       <c r="BB91" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="92" spans="54:54">
       <c r="BB92" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="93" spans="54:54">
       <c r="BB93" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="94" spans="54:54">
       <c r="BB94" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="95" spans="54:54">
       <c r="BB95" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="96" spans="54:54">
       <c r="BB96" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="97" spans="54:54">
       <c r="BB97" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="98" spans="54:54">
       <c r="BB98" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="99" spans="54:54">
       <c r="BB99" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="100" spans="54:54">
       <c r="BB100" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="101" spans="54:54">
       <c r="BB101" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="102" spans="54:54">
       <c r="BB102" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="103" spans="54:54">
       <c r="BB103" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="104" spans="54:54">
       <c r="BB104" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="54:54">
       <c r="BB105" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="106" spans="54:54">
       <c r="BB106" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="107" spans="54:54">
       <c r="BB107" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108" spans="54:54">
       <c r="BB108" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="109" spans="54:54">
       <c r="BB109" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="110" spans="54:54">
       <c r="BB110" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="111" spans="54:54">
       <c r="BB111" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="112" spans="54:54">
       <c r="BB112" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="113" spans="54:54">
       <c r="BB113" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="114" spans="54:54">
       <c r="BB114" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="115" spans="54:54">
       <c r="BB115" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="116" spans="54:54">
       <c r="BB116" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="117" spans="54:54">
       <c r="BB117" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="118" spans="54:54">
       <c r="BB118" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="119" spans="54:54">
       <c r="BB119" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="120" spans="54:54">
       <c r="BB120" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="121" spans="54:54">
       <c r="BB121" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="122" spans="54:54">
       <c r="BB122" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="123" spans="54:54">
       <c r="BB123" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="124" spans="54:54">
       <c r="BB124" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="125" spans="54:54">
       <c r="BB125" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="126" spans="54:54">
       <c r="BB126" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="127" spans="54:54">
       <c r="BB127" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="128" spans="54:54">
       <c r="BB128" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="129" spans="54:54">
       <c r="BB129" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="130" spans="54:54">
       <c r="BB130" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="131" spans="54:54">
       <c r="BB131" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="132" spans="54:54">
       <c r="BB132" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="133" spans="54:54">
       <c r="BB133" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="134" spans="54:54">
       <c r="BB134" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="135" spans="54:54">
       <c r="BB135" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="136" spans="54:54">
       <c r="BB136" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="137" spans="54:54">
       <c r="BB137" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="138" spans="54:54">
       <c r="BB138" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="139" spans="54:54">
       <c r="BB139" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="140" spans="54:54">
       <c r="BB140" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="141" spans="54:54">
       <c r="BB141" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="142" spans="54:54">
       <c r="BB142" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="143" spans="54:54">
       <c r="BB143" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="144" spans="54:54">
       <c r="BB144" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="145" spans="54:54">
       <c r="BB145" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="146" spans="54:54">
       <c r="BB146" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="147" spans="54:54">
       <c r="BB147" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="148" spans="54:54">
       <c r="BB148" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="149" spans="54:54">
       <c r="BB149" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="150" spans="54:54">
       <c r="BB150" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="151" spans="54:54">
       <c r="BB151" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="152" spans="54:54">
       <c r="BB152" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="153" spans="54:54">
       <c r="BB153" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="154" spans="54:54">
       <c r="BB154" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="155" spans="54:54">
       <c r="BB155" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="156" spans="54:54">
       <c r="BB156" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="157" spans="54:54">
       <c r="BB157" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="158" spans="54:54">
       <c r="BB158" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="159" spans="54:54">
       <c r="BB159" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="160" spans="54:54">
       <c r="BB160" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="161" spans="54:54">
       <c r="BB161" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="162" spans="54:54">
       <c r="BB162" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="163" spans="54:54">
       <c r="BB163" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="164" spans="54:54">
       <c r="BB164" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="165" spans="54:54">
       <c r="BB165" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="166" spans="54:54">
       <c r="BB166" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="167" spans="54:54">
       <c r="BB167" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="168" spans="54:54">
       <c r="BB168" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="169" spans="54:54">
       <c r="BB169" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="170" spans="54:54">
       <c r="BB170" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="171" spans="54:54">
       <c r="BB171" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="172" spans="54:54">
       <c r="BB172" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="173" spans="54:54">
       <c r="BB173" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="174" spans="54:54">
       <c r="BB174" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="175" spans="54:54">
       <c r="BB175" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="176" spans="54:54">
       <c r="BB176" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="177" spans="54:54">
       <c r="BB177" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="178" spans="54:54">
       <c r="BB178" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="179" spans="54:54">
       <c r="BB179" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="180" spans="54:54">
       <c r="BB180" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="181" spans="54:54">
       <c r="BB181" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="182" spans="54:54">
       <c r="BB182" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="183" spans="54:54">
       <c r="BB183" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="184" spans="54:54">
       <c r="BB184" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="185" spans="54:54">
       <c r="BB185" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="186" spans="54:54">
       <c r="BB186" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="187" spans="54:54">
       <c r="BB187" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="188" spans="54:54">
       <c r="BB188" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="189" spans="54:54">
       <c r="BB189" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="190" spans="54:54">
       <c r="BB190" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="191" spans="54:54">
       <c r="BB191" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" spans="54:54">
       <c r="BB192" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="193" spans="54:54">
       <c r="BB193" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="194" spans="54:54">
       <c r="BB194" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="195" spans="54:54">
       <c r="BB195" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="196" spans="54:54">
       <c r="BB196" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="197" spans="54:54">
       <c r="BB197" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="198" spans="54:54">
       <c r="BB198" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="199" spans="54:54">
       <c r="BB199" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="200" spans="54:54">
       <c r="BB200" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="201" spans="54:54">
       <c r="BB201" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="202" spans="54:54">
       <c r="BB202" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="203" spans="54:54">
       <c r="BB203" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="204" spans="54:54">
       <c r="BB204" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="205" spans="54:54">
       <c r="BB205" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="206" spans="54:54">
       <c r="BB206" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="207" spans="54:54">
       <c r="BB207" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="208" spans="54:54">
       <c r="BB208" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="209" spans="54:54">
       <c r="BB209" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="210" spans="54:54">
       <c r="BB210" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="211" spans="54:54">
       <c r="BB211" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="212" spans="54:54">
       <c r="BB212" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="213" spans="54:54">
       <c r="BB213" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="214" spans="54:54">
       <c r="BB214" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="215" spans="54:54">
       <c r="BB215" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="216" spans="54:54">
       <c r="BB216" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="217" spans="54:54">
       <c r="BB217" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="218" spans="54:54">
       <c r="BB218" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="219" spans="54:54">
       <c r="BB219" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="220" spans="54:54">
       <c r="BB220" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="54:54">
       <c r="BB221" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="222" spans="54:54">
       <c r="BB222" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="223" spans="54:54">
       <c r="BB223" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="224" spans="54:54">
       <c r="BB224" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="225" spans="54:54">
       <c r="BB225" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="226" spans="54:54">
       <c r="BB226" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="227" spans="54:54">
       <c r="BB227" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="228" spans="54:54">
       <c r="BB228" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="229" spans="54:54">
       <c r="BB229" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="230" spans="54:54">
       <c r="BB230" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="231" spans="54:54">
       <c r="BB231" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="232" spans="54:54">
       <c r="BB232" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="233" spans="54:54">
       <c r="BB233" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="234" spans="54:54">
       <c r="BB234" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="235" spans="54:54">
       <c r="BB235" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="236" spans="54:54">
       <c r="BB236" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="237" spans="54:54">
       <c r="BB237" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="238" spans="54:54">
       <c r="BB238" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="239" spans="54:54">
       <c r="BB239" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="240" spans="54:54">
       <c r="BB240" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="241" spans="54:54">
       <c r="BB241" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="242" spans="54:54">
       <c r="BB242" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="243" spans="54:54">
       <c r="BB243" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="244" spans="54:54">
       <c r="BB244" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="245" spans="54:54">
       <c r="BB245" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="246" spans="54:54">
       <c r="BB246" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="247" spans="54:54">
       <c r="BB247" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="248" spans="54:54">
       <c r="BB248" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="249" spans="54:54">
       <c r="BB249" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="250" spans="54:54">
       <c r="BB250" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="251" spans="54:54">
       <c r="BB251" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="252" spans="54:54">
       <c r="BB252" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="253" spans="54:54">
       <c r="BB253" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="254" spans="54:54">
       <c r="BB254" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="255" spans="54:54">
       <c r="BB255" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="256" spans="54:54">
       <c r="BB256" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="257" spans="54:54">
       <c r="BB257" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="258" spans="54:54">
       <c r="BB258" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="259" spans="54:54">
       <c r="BB259" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="260" spans="54:54">
       <c r="BB260" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="261" spans="54:54">
       <c r="BB261" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="262" spans="54:54">
       <c r="BB262" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="263" spans="54:54">
       <c r="BB263" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="264" spans="54:54">
       <c r="BB264" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="265" spans="54:54">
       <c r="BB265" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="266" spans="54:54">
       <c r="BB266" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="267" spans="54:54">
       <c r="BB267" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="268" spans="54:54">
       <c r="BB268" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="269" spans="54:54">
       <c r="BB269" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="270" spans="54:54">
       <c r="BB270" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="271" spans="54:54">
       <c r="BB271" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="272" spans="54:54">
       <c r="BB272" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="273" spans="54:54">
       <c r="BB273" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="274" spans="54:54">
       <c r="BB274" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="275" spans="54:54">
       <c r="BB275" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="276" spans="54:54">
       <c r="BB276" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="277" spans="54:54">
       <c r="BB277" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="278" spans="54:54">
       <c r="BB278" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="279" spans="54:54">
       <c r="BB279" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="280" spans="54:54">
       <c r="BB280" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="281" spans="54:54">
       <c r="BB281" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="282" spans="54:54">
       <c r="BB282" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="283" spans="54:54">
       <c r="BB283" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="284" spans="54:54">
       <c r="BB284" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="285" spans="54:54">
       <c r="BB285" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="286" spans="54:54">
       <c r="BB286" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="287" spans="54:54">
       <c r="BB287" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="288" spans="54:54">
       <c r="BB288" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="289" spans="54:54">
       <c r="BB289" t="s">
-        <v>710</v>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="290" spans="54:54">
+      <c r="BB290" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="291" spans="54:54">
+      <c r="BB291" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="292" spans="54:54">
+      <c r="BB292" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="293" spans="54:54">
+      <c r="BB293" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="294" spans="54:54">
+      <c r="BB294" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000037/metadata_template_ERC000037.xlsx
+++ b/templates/ERC000037/metadata_template_ERC000037.xlsx
@@ -22,7 +22,7 @@
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$BB$1:$BB$294</definedName>
     <definedName name="growthfacility">'cv_sample'!$T$1:$T$6</definedName>
     <definedName name="growthhabit">'cv_sample'!$AX$1:$AX$4</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="829">
   <si>
     <t>alias</t>
   </si>
@@ -734,6 +734,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -3051,7 +3054,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3095,7 +3098,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3122,7 +3125,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3859,6 +3862,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3880,27 +3888,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3920,122 +3928,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4059,630 +4067,630 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="2" spans="1:105" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -4723,1658 +4731,1658 @@
   <sheetData>
     <row r="1" spans="7:58">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="T1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="W1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AU1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AX1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BB1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="BF1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2" spans="7:58">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="T2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="W2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AU2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AX2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="BB2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="BF2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3" spans="7:58">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AU3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AX3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="BB3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="BF3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="7:58">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AU4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AX4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="BB4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="BF4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="7:58">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AU5" t="s">
         <v>116</v>
       </c>
       <c r="BB5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="BF5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6" spans="7:58">
       <c r="O6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="T6" t="s">
         <v>116</v>
       </c>
       <c r="AU6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BB6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="BF6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7" spans="7:58">
       <c r="O7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AU7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="BB7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="7:58">
       <c r="O8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BB8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="7:58">
       <c r="O9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BB9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="7:58">
       <c r="O10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BB10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" spans="7:58">
       <c r="O11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BB11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="7:58">
       <c r="O12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BB12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="7:58">
       <c r="O13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="BB13" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="7:58">
       <c r="O14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BB14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="7:58">
       <c r="O15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="BB15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="7:58">
       <c r="O16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BB16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="15:54">
       <c r="O17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BB17" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="15:54">
       <c r="O18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="BB18" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="15:54">
       <c r="O19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BB19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="15:54">
       <c r="O20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="BB20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="15:54">
       <c r="O21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BB21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" spans="15:54">
       <c r="O22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="BB22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="23" spans="15:54">
       <c r="O23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="BB23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="15:54">
       <c r="O24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="BB24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" spans="15:54">
       <c r="O25" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="BB25" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="15:54">
       <c r="O26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="BB26" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="15:54">
       <c r="O27" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BB27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="15:54">
       <c r="O28" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="BB28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" spans="15:54">
       <c r="O29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="BB29" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="15:54">
       <c r="O30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="BB30" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="15:54">
       <c r="O31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="BB31" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="15:54">
       <c r="O32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="BB32" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="54:54">
       <c r="BB33" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="54:54">
       <c r="BB34" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="35" spans="54:54">
       <c r="BB35" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="36" spans="54:54">
       <c r="BB36" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" spans="54:54">
       <c r="BB37" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38" spans="54:54">
       <c r="BB38" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="39" spans="54:54">
       <c r="BB39" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="54:54">
       <c r="BB40" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="54:54">
       <c r="BB41" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="42" spans="54:54">
       <c r="BB42" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="43" spans="54:54">
       <c r="BB43" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44" spans="54:54">
       <c r="BB44" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="45" spans="54:54">
       <c r="BB45" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46" spans="54:54">
       <c r="BB46" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="47" spans="54:54">
       <c r="BB47" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" spans="54:54">
       <c r="BB48" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="49" spans="54:54">
       <c r="BB49" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="50" spans="54:54">
       <c r="BB50" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="51" spans="54:54">
       <c r="BB51" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="54:54">
       <c r="BB52" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="53" spans="54:54">
       <c r="BB53" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="54" spans="54:54">
       <c r="BB54" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="54:54">
       <c r="BB55" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="54:54">
       <c r="BB56" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="54:54">
       <c r="BB57" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" spans="54:54">
       <c r="BB58" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="59" spans="54:54">
       <c r="BB59" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="60" spans="54:54">
       <c r="BB60" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="61" spans="54:54">
       <c r="BB61" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="62" spans="54:54">
       <c r="BB62" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="63" spans="54:54">
       <c r="BB63" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="64" spans="54:54">
       <c r="BB64" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="65" spans="54:54">
       <c r="BB65" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="66" spans="54:54">
       <c r="BB66" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="67" spans="54:54">
       <c r="BB67" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="68" spans="54:54">
       <c r="BB68" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="69" spans="54:54">
       <c r="BB69" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="70" spans="54:54">
       <c r="BB70" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="71" spans="54:54">
       <c r="BB71" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="72" spans="54:54">
       <c r="BB72" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="73" spans="54:54">
       <c r="BB73" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="74" spans="54:54">
       <c r="BB74" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="75" spans="54:54">
       <c r="BB75" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="54:54">
       <c r="BB76" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="54:54">
       <c r="BB77" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="78" spans="54:54">
       <c r="BB78" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="79" spans="54:54">
       <c r="BB79" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="80" spans="54:54">
       <c r="BB80" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="81" spans="54:54">
       <c r="BB81" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="82" spans="54:54">
       <c r="BB82" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="83" spans="54:54">
       <c r="BB83" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="84" spans="54:54">
       <c r="BB84" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="85" spans="54:54">
       <c r="BB85" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="86" spans="54:54">
       <c r="BB86" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="87" spans="54:54">
       <c r="BB87" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="88" spans="54:54">
       <c r="BB88" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="89" spans="54:54">
       <c r="BB89" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="90" spans="54:54">
       <c r="BB90" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="91" spans="54:54">
       <c r="BB91" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="92" spans="54:54">
       <c r="BB92" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="93" spans="54:54">
       <c r="BB93" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="94" spans="54:54">
       <c r="BB94" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="95" spans="54:54">
       <c r="BB95" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="96" spans="54:54">
       <c r="BB96" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="97" spans="54:54">
       <c r="BB97" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="98" spans="54:54">
       <c r="BB98" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="99" spans="54:54">
       <c r="BB99" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="100" spans="54:54">
       <c r="BB100" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="101" spans="54:54">
       <c r="BB101" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="102" spans="54:54">
       <c r="BB102" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="103" spans="54:54">
       <c r="BB103" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104" spans="54:54">
       <c r="BB104" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="105" spans="54:54">
       <c r="BB105" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="106" spans="54:54">
       <c r="BB106" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="107" spans="54:54">
       <c r="BB107" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="108" spans="54:54">
       <c r="BB108" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="109" spans="54:54">
       <c r="BB109" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="110" spans="54:54">
       <c r="BB110" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="111" spans="54:54">
       <c r="BB111" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="112" spans="54:54">
       <c r="BB112" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="113" spans="54:54">
       <c r="BB113" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="114" spans="54:54">
       <c r="BB114" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="115" spans="54:54">
       <c r="BB115" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="116" spans="54:54">
       <c r="BB116" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="117" spans="54:54">
       <c r="BB117" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="118" spans="54:54">
       <c r="BB118" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="119" spans="54:54">
       <c r="BB119" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="120" spans="54:54">
       <c r="BB120" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="121" spans="54:54">
       <c r="BB121" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="122" spans="54:54">
       <c r="BB122" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="123" spans="54:54">
       <c r="BB123" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="124" spans="54:54">
       <c r="BB124" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="125" spans="54:54">
       <c r="BB125" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="126" spans="54:54">
       <c r="BB126" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="127" spans="54:54">
       <c r="BB127" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="128" spans="54:54">
       <c r="BB128" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="129" spans="54:54">
       <c r="BB129" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="130" spans="54:54">
       <c r="BB130" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="131" spans="54:54">
       <c r="BB131" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="132" spans="54:54">
       <c r="BB132" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="133" spans="54:54">
       <c r="BB133" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="134" spans="54:54">
       <c r="BB134" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="135" spans="54:54">
       <c r="BB135" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="136" spans="54:54">
       <c r="BB136" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="137" spans="54:54">
       <c r="BB137" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="138" spans="54:54">
       <c r="BB138" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="139" spans="54:54">
       <c r="BB139" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="140" spans="54:54">
       <c r="BB140" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="141" spans="54:54">
       <c r="BB141" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="142" spans="54:54">
       <c r="BB142" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="143" spans="54:54">
       <c r="BB143" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="144" spans="54:54">
       <c r="BB144" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="145" spans="54:54">
       <c r="BB145" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="146" spans="54:54">
       <c r="BB146" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="147" spans="54:54">
       <c r="BB147" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="148" spans="54:54">
       <c r="BB148" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="149" spans="54:54">
       <c r="BB149" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="150" spans="54:54">
       <c r="BB150" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="151" spans="54:54">
       <c r="BB151" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="152" spans="54:54">
       <c r="BB152" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="153" spans="54:54">
       <c r="BB153" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="154" spans="54:54">
       <c r="BB154" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="155" spans="54:54">
       <c r="BB155" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="156" spans="54:54">
       <c r="BB156" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="157" spans="54:54">
       <c r="BB157" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="158" spans="54:54">
       <c r="BB158" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="159" spans="54:54">
       <c r="BB159" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="160" spans="54:54">
       <c r="BB160" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="161" spans="54:54">
       <c r="BB161" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="162" spans="54:54">
       <c r="BB162" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="163" spans="54:54">
       <c r="BB163" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="164" spans="54:54">
       <c r="BB164" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="165" spans="54:54">
       <c r="BB165" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="166" spans="54:54">
       <c r="BB166" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="167" spans="54:54">
       <c r="BB167" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="168" spans="54:54">
       <c r="BB168" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="169" spans="54:54">
       <c r="BB169" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="170" spans="54:54">
       <c r="BB170" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="171" spans="54:54">
       <c r="BB171" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="172" spans="54:54">
       <c r="BB172" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="173" spans="54:54">
       <c r="BB173" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="174" spans="54:54">
       <c r="BB174" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="175" spans="54:54">
       <c r="BB175" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="176" spans="54:54">
       <c r="BB176" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="177" spans="54:54">
       <c r="BB177" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="178" spans="54:54">
       <c r="BB178" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="179" spans="54:54">
       <c r="BB179" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="180" spans="54:54">
       <c r="BB180" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="181" spans="54:54">
       <c r="BB181" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="182" spans="54:54">
       <c r="BB182" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="183" spans="54:54">
       <c r="BB183" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="184" spans="54:54">
       <c r="BB184" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="185" spans="54:54">
       <c r="BB185" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="186" spans="54:54">
       <c r="BB186" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="187" spans="54:54">
       <c r="BB187" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="188" spans="54:54">
       <c r="BB188" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="189" spans="54:54">
       <c r="BB189" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="190" spans="54:54">
       <c r="BB190" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="191" spans="54:54">
       <c r="BB191" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="192" spans="54:54">
       <c r="BB192" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="193" spans="54:54">
       <c r="BB193" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="194" spans="54:54">
       <c r="BB194" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="195" spans="54:54">
       <c r="BB195" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="196" spans="54:54">
       <c r="BB196" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="197" spans="54:54">
       <c r="BB197" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="198" spans="54:54">
       <c r="BB198" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="199" spans="54:54">
       <c r="BB199" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="200" spans="54:54">
       <c r="BB200" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="201" spans="54:54">
       <c r="BB201" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="202" spans="54:54">
       <c r="BB202" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="203" spans="54:54">
       <c r="BB203" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="204" spans="54:54">
       <c r="BB204" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="205" spans="54:54">
       <c r="BB205" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="206" spans="54:54">
       <c r="BB206" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="207" spans="54:54">
       <c r="BB207" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="208" spans="54:54">
       <c r="BB208" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="209" spans="54:54">
       <c r="BB209" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="210" spans="54:54">
       <c r="BB210" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="211" spans="54:54">
       <c r="BB211" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="212" spans="54:54">
       <c r="BB212" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="213" spans="54:54">
       <c r="BB213" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="214" spans="54:54">
       <c r="BB214" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="215" spans="54:54">
       <c r="BB215" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="216" spans="54:54">
       <c r="BB216" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="217" spans="54:54">
       <c r="BB217" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="218" spans="54:54">
       <c r="BB218" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="219" spans="54:54">
       <c r="BB219" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="220" spans="54:54">
       <c r="BB220" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="221" spans="54:54">
       <c r="BB221" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="222" spans="54:54">
       <c r="BB222" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="223" spans="54:54">
       <c r="BB223" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="224" spans="54:54">
       <c r="BB224" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="225" spans="54:54">
       <c r="BB225" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="226" spans="54:54">
       <c r="BB226" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="227" spans="54:54">
       <c r="BB227" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="228" spans="54:54">
       <c r="BB228" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="229" spans="54:54">
       <c r="BB229" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="230" spans="54:54">
       <c r="BB230" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="231" spans="54:54">
       <c r="BB231" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="232" spans="54:54">
       <c r="BB232" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="233" spans="54:54">
       <c r="BB233" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="234" spans="54:54">
       <c r="BB234" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="235" spans="54:54">
       <c r="BB235" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="236" spans="54:54">
       <c r="BB236" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="237" spans="54:54">
       <c r="BB237" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="238" spans="54:54">
       <c r="BB238" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="239" spans="54:54">
       <c r="BB239" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="240" spans="54:54">
       <c r="BB240" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="241" spans="54:54">
       <c r="BB241" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="242" spans="54:54">
       <c r="BB242" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="243" spans="54:54">
       <c r="BB243" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="244" spans="54:54">
       <c r="BB244" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="245" spans="54:54">
       <c r="BB245" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="246" spans="54:54">
       <c r="BB246" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="247" spans="54:54">
       <c r="BB247" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="248" spans="54:54">
       <c r="BB248" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="249" spans="54:54">
       <c r="BB249" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="250" spans="54:54">
       <c r="BB250" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="251" spans="54:54">
       <c r="BB251" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="252" spans="54:54">
       <c r="BB252" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="253" spans="54:54">
       <c r="BB253" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="254" spans="54:54">
       <c r="BB254" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="255" spans="54:54">
       <c r="BB255" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="256" spans="54:54">
       <c r="BB256" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="257" spans="54:54">
       <c r="BB257" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="258" spans="54:54">
       <c r="BB258" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="259" spans="54:54">
       <c r="BB259" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="260" spans="54:54">
       <c r="BB260" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="261" spans="54:54">
       <c r="BB261" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="262" spans="54:54">
       <c r="BB262" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="263" spans="54:54">
       <c r="BB263" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="264" spans="54:54">
       <c r="BB264" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="265" spans="54:54">
       <c r="BB265" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="266" spans="54:54">
       <c r="BB266" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="267" spans="54:54">
       <c r="BB267" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="268" spans="54:54">
       <c r="BB268" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="269" spans="54:54">
       <c r="BB269" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="270" spans="54:54">
       <c r="BB270" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="271" spans="54:54">
       <c r="BB271" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="272" spans="54:54">
       <c r="BB272" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="273" spans="54:54">
       <c r="BB273" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="274" spans="54:54">
       <c r="BB274" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="275" spans="54:54">
       <c r="BB275" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="276" spans="54:54">
       <c r="BB276" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="277" spans="54:54">
       <c r="BB277" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="278" spans="54:54">
       <c r="BB278" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="279" spans="54:54">
       <c r="BB279" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="280" spans="54:54">
       <c r="BB280" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="281" spans="54:54">
       <c r="BB281" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="282" spans="54:54">
       <c r="BB282" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="283" spans="54:54">
       <c r="BB283" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="284" spans="54:54">
       <c r="BB284" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="285" spans="54:54">
       <c r="BB285" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="286" spans="54:54">
       <c r="BB286" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="287" spans="54:54">
       <c r="BB287" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="288" spans="54:54">
       <c r="BB288" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="289" spans="54:54">
       <c r="BB289" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="290" spans="54:54">
       <c r="BB290" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="291" spans="54:54">
       <c r="BB291" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="292" spans="54:54">
       <c r="BB292" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="293" spans="54:54">
       <c r="BB293" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="294" spans="54:54">
       <c r="BB294" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
